--- a/2026/COLOMBRES/Marzo/Marzo COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/Marzo/Marzo COLOMBRES 360.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\COLOMBRES\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\COLOMBRES\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6077C3D6-6827-4D6C-9B2F-97A7FE857837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5713B3A-1550-4D55-B5B9-F1CA50C1FDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$133</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="188">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -403,9 +408,6 @@
     <t xml:space="preserve">METROGAS - Cliente 30008873781 </t>
   </si>
   <si>
-    <t>Banco Supervielle  - Gastos bancarios</t>
-  </si>
-  <si>
     <t xml:space="preserve">Allianz Argentina - Póliza 240170531675 - Vida colectivo </t>
   </si>
   <si>
@@ -431,9 +433,6 @@
   </si>
   <si>
     <t xml:space="preserve">EDESUR - Cliente 80089864 </t>
-  </si>
-  <si>
-    <t>Banco Supervielle - Mantenimiento cuenta corriente</t>
   </si>
   <si>
     <t xml:space="preserve">AySA - Cuenta 1266646 </t>
@@ -473,69 +472,18 @@
     <t>HORARIOS DE ATENCION: 10 A 15HS - LUNES A VIERNES</t>
   </si>
   <si>
-    <t>Servicio de fumigacion - Ortega Daniel - Mes de Octubre - Se adeudaba</t>
-  </si>
-  <si>
-    <t>Loschi Bruno - Mantenimiento bimestral</t>
-  </si>
-  <si>
-    <t>Transf 30/01</t>
-  </si>
-  <si>
     <t>PABLO GARCIA - MATIAS EZEQUIEL GARCIA</t>
   </si>
   <si>
-    <t>Deposito sin identificar del - 15/01</t>
-  </si>
-  <si>
     <t>Los depositos sin identificar del 15/01 son de sergio</t>
   </si>
   <si>
     <t>El 1B mando un mail desde soniases2020@icloud.com para que verifiquemos que no tiene deuda alguno, mando todos sus comprobantes desde hace mucho tiempo 226497,02 - Deben abonar    337.700,02</t>
   </si>
   <si>
-    <t>Transf 04/02</t>
-  </si>
-  <si>
-    <t>Debito 04/02</t>
-  </si>
-  <si>
-    <t>Debito 12/02</t>
-  </si>
-  <si>
-    <t>Cerrajeria Ayram - 1 Microllavero - Sr. Diego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transf 10/02 </t>
-  </si>
-  <si>
-    <t>Vacaciones abonadas - Trabajadas</t>
-  </si>
-  <si>
-    <t>Transf 20/02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adelanto vacaciones </t>
-  </si>
-  <si>
-    <t>Transf 18/02</t>
-  </si>
-  <si>
-    <t>Transf 23/02</t>
-  </si>
-  <si>
-    <t>Escribania Romanatti - Digitalizacion para presentar en ARCA</t>
-  </si>
-  <si>
     <t>Efectivo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ferreteria Beta - Compra de acoples </t>
-  </si>
-  <si>
-    <t>Deposito ya identificado mes anterior</t>
-  </si>
-  <si>
     <t>Punitorios mal cobrados 4A</t>
   </si>
   <si>
@@ -543,12 +491,6 @@
   </si>
   <si>
     <t>Guenaga Gonzalo Federico</t>
-  </si>
-  <si>
-    <t>Seguro Mercantil Andina - Sra Patricia Reemplazo vacaciones Diego</t>
-  </si>
-  <si>
-    <t>Debito 25/02</t>
   </si>
   <si>
     <t>2-A - MAGRO LAUTARO - MAGRO DANIELA - CUOTA 1/6 PLAN DE PAGOS</t>
@@ -567,9 +509,6 @@
     <t>Mes de MARZO</t>
   </si>
   <si>
-    <t>MARZO</t>
-  </si>
-  <si>
     <t>Frank Matias Wallace - Mantenimiento ascensor MARZO</t>
   </si>
   <si>
@@ -585,25 +524,96 @@
     <t>Transf 16/03</t>
   </si>
   <si>
-    <t>Maria Celeste Basile</t>
-  </si>
-  <si>
     <t>Transf 19/03</t>
   </si>
   <si>
     <t>Transf 12/03</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado mes Enero (mal restados en expensas de Febrero)</t>
+  </si>
+  <si>
+    <t>Debito 09/03</t>
+  </si>
+  <si>
+    <t>Pago de deuda (capital)</t>
+  </si>
+  <si>
+    <t>Debito 10/03</t>
+  </si>
+  <si>
+    <t>Sotelo Gladys Patricia - Reemplazo Sr. Diego Calderon</t>
+  </si>
+  <si>
+    <t>Seguro Federacion Patronal - Seguro de consorcio - Poliza nro. 2290715</t>
+  </si>
+  <si>
+    <t>Debito 19/03</t>
+  </si>
+  <si>
+    <t>Maria Celeste Basile - Diferencia pedido 3er testimonio de reglamento</t>
+  </si>
+  <si>
+    <t>Loschi Bruno - Mantenimiento bimestral - Grupo electrogeno</t>
+  </si>
+  <si>
+    <t>Transf 25/03</t>
+  </si>
+  <si>
+    <t>Debito 05/03</t>
+  </si>
+  <si>
+    <t>Debito 12/03</t>
+  </si>
+  <si>
+    <t>Allianz Consorcio Poliza - Debito poliza mes anterior (Febrero) - Se debita ultima cuota de esta poliza</t>
+  </si>
+  <si>
+    <t>Debito 16/03</t>
+  </si>
+  <si>
+    <t>Banco  - Gastos bancarios</t>
+  </si>
+  <si>
+    <t>Servicio de fumigacion - Ortega Daniel</t>
+  </si>
+  <si>
+    <t>Transf 27/03</t>
+  </si>
+  <si>
+    <t>Gustavo Padron Sr Contador - Balance anual pedido por RPAC</t>
+  </si>
+  <si>
+    <t>Tofema - compra de portalamparas y lamapra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricista - Reemplazo de portalampras y lampraras </t>
+  </si>
+  <si>
+    <t>Transf 30/03</t>
+  </si>
+  <si>
+    <t>Se adeuda Marzo</t>
+  </si>
+  <si>
+    <t>Banco - Mantenimiento cuenta corriente - Supervielle por cierre ya que no estaba la chequwera y hubo que denunciar los cheques</t>
+  </si>
+  <si>
+    <t>Bonificacion bancaria por parte de Santander</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -880,7 +890,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1222,22 +1232,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1394,9 +1395,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1430,29 +1428,13 @@
     <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1472,6 +1454,48 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1487,47 +1511,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1541,67 +1574,16 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1670,9 +1652,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1710,9 +1692,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1745,9 +1727,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1780,9 +1779,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1956,20 +1972,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L137"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L131"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
         <v>122</v>
       </c>
@@ -1977,7 +1994,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="109" t="s">
         <v>123</v>
       </c>
@@ -1985,84 +2002,84 @@
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
     </row>
-    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="109" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B3" s="109"/>
       <c r="C3" s="109"/>
       <c r="D3" s="109"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="181" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="181"/>
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="162" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="162"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="181"/>
-      <c r="B5" s="181"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="162"/>
+      <c r="B5" s="162"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="181"/>
-      <c r="B6" s="181"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="162"/>
+      <c r="B6" s="162"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="181"/>
-      <c r="B7" s="181"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="162"/>
+      <c r="B7" s="162"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="180" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="180"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="180"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="182" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="159" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="159"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="159"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="163" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="182"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="182"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="182"/>
-      <c r="B15" s="182"/>
-      <c r="C15" s="182"/>
-      <c r="D15" s="182"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="182"/>
-      <c r="B16" s="182"/>
-      <c r="C16" s="182"/>
-      <c r="D16" s="182"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="182"/>
-      <c r="B17" s="182"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="163"/>
+      <c r="C14" s="163"/>
+      <c r="D14" s="163"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="163"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="163"/>
+      <c r="D15" s="163"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="163"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="163"/>
+      <c r="D16" s="163"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="163"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="163"/>
+      <c r="D17" s="163"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2070,7 +2087,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>80</v>
       </c>
@@ -2078,1065 +2095,998 @@
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C23" s="137">
-        <v>1497939.7</v>
+        <v>156</v>
+      </c>
+      <c r="C23" s="136">
+        <v>1603651.83</v>
       </c>
       <c r="D23" s="80"/>
-      <c r="G23" s="159"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="137">
-        <v>-618836.34</v>
+      <c r="C24" s="136">
+        <v>-820908.27</v>
       </c>
       <c r="D24" s="80"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="137">
-        <v>0.64</v>
+      <c r="C25" s="136">
+        <v>0.44</v>
       </c>
       <c r="D25" s="80"/>
-      <c r="G25" s="14"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>162</v>
-      </c>
+      <c r="G25" s="152"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="137">
-        <v>422400</v>
-      </c>
+      <c r="C26" s="136"/>
       <c r="D26" s="80"/>
-      <c r="G26" s="14"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="47" t="s">
         <v>82</v>
       </c>
       <c r="B27" s="47"/>
       <c r="C27" s="106">
         <f>SUM(C23:C26)</f>
-        <v>1301504</v>
+        <v>782744</v>
       </c>
       <c r="D27" s="47"/>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C28" s="137">
-        <v>1232039.3</v>
-      </c>
-      <c r="D28" s="80"/>
-      <c r="G28" s="14"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+      <c r="C28" s="136">
+        <v>1547614.11</v>
+      </c>
+      <c r="D28" s="113"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="137">
-        <v>-267968.53999999998</v>
-      </c>
-      <c r="D29" s="80"/>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C29" s="136">
+        <v>-336606.06</v>
+      </c>
+      <c r="D29" s="113"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="137">
-        <v>0.24</v>
-      </c>
-      <c r="D30" s="80"/>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>160</v>
-      </c>
+      <c r="C30" s="136">
+        <v>0.95</v>
+      </c>
+      <c r="D30" s="113"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="150">
-        <v>633951.69999999995</v>
-      </c>
-      <c r="D31" s="80"/>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C31" s="198"/>
+      <c r="D31" s="113"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="47"/>
-      <c r="C32" s="106">
+      <c r="B32" s="112"/>
+      <c r="C32" s="48">
         <f>SUM(C28:C31)</f>
-        <v>1598022.7</v>
+        <v>1211009</v>
       </c>
       <c r="D32" s="81"/>
-      <c r="F32" s="178"/>
-      <c r="G32" s="179"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C33" s="137">
-        <v>554812.06999999995</v>
+        <v>156</v>
+      </c>
+      <c r="C33" s="136">
+        <v>1232494.5</v>
       </c>
       <c r="D33" s="113"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="137">
-        <v>-120671.62</v>
+      <c r="C34" s="136">
+        <v>-268067.53000000003</v>
       </c>
       <c r="D34" s="113"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="137">
-        <v>0.55000000000000004</v>
+      <c r="C35" s="136">
+        <v>0.03</v>
       </c>
       <c r="D35" s="113"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="150"/>
+      <c r="C36" s="198"/>
       <c r="D36" s="113"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
         <v>82</v>
       </c>
       <c r="B37" s="112"/>
       <c r="C37" s="48">
         <f>SUM(C33:C36)</f>
-        <v>434140.99999999994</v>
+        <v>964427</v>
       </c>
       <c r="D37" s="81"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F37" s="14"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C38" s="137">
-        <v>1578850.12</v>
-      </c>
-      <c r="D38" s="80"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="198">
+        <f>175000+300000+331000</f>
+        <v>806000</v>
+      </c>
+      <c r="D38" s="113"/>
+      <c r="F38" s="14"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="137">
-        <v>-810662.45</v>
-      </c>
-      <c r="D39" s="80"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="C39" s="198"/>
+      <c r="D39" s="113"/>
+      <c r="F39" s="14"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="137">
-        <v>0.33</v>
-      </c>
-      <c r="D40" s="80"/>
-      <c r="G40" s="159"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C40" s="198"/>
+      <c r="D40" s="113"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="137"/>
-      <c r="D41" s="80"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="197"/>
+      <c r="C41" s="198"/>
+      <c r="D41" s="113"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="47"/>
-      <c r="C42" s="106">
+      <c r="B42" s="112"/>
+      <c r="C42" s="48">
         <f>SUM(C38:C41)</f>
-        <v>768188.00000000012</v>
-      </c>
-      <c r="D42" s="47"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B43" s="5" t="s">
+        <v>806000</v>
+      </c>
+      <c r="D42" s="81"/>
+    </row>
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="82">
+        <f>+C27+C32+C42+C37</f>
+        <v>3764180</v>
+      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="26"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="83"/>
+      <c r="F44" s="14"/>
+    </row>
+    <row r="45" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="136">
+        <v>135000</v>
+      </c>
+      <c r="D45" s="123" t="s">
+        <v>161</v>
+      </c>
+      <c r="G45" s="14"/>
+    </row>
+    <row r="46" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" s="200"/>
+      <c r="C46" s="136">
+        <v>150000</v>
+      </c>
+      <c r="D46" s="123"/>
+      <c r="G46" s="14"/>
+    </row>
+    <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="107" t="s">
+        <v>185</v>
+      </c>
+      <c r="C47" s="136">
+        <v>0</v>
+      </c>
+      <c r="D47" s="123"/>
+      <c r="G47" s="14"/>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="82">
+        <f>SUM(C45:C47)</f>
+        <v>285000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" s="25"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="57"/>
+    </row>
+    <row r="50" spans="1:6" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="160" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" s="161"/>
+      <c r="C50" s="155">
+        <v>125266</v>
+      </c>
+      <c r="D50" s="153" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="160" t="s">
+        <v>176</v>
+      </c>
+      <c r="B51" s="161"/>
+      <c r="C51" s="155">
+        <v>220076.23</v>
+      </c>
+      <c r="D51" s="153" t="s">
         <v>177</v>
       </c>
-      <c r="C43" s="137">
-        <v>1433185.66</v>
-      </c>
-      <c r="D43" s="113"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="137">
-        <v>-311717.88</v>
-      </c>
-      <c r="D44" s="113"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="137">
-        <v>0.22</v>
-      </c>
-      <c r="D45" s="113"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="150"/>
-      <c r="D46" s="113"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="112"/>
-      <c r="C47" s="48">
-        <f>SUM(C43:C46)</f>
-        <v>1121467.9999999998</v>
-      </c>
-      <c r="D47" s="81"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
+    </row>
+    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="160" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="161"/>
+      <c r="C52" s="156">
+        <v>4203</v>
+      </c>
+      <c r="D52" s="122" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53" s="25"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="84">
+        <f>SUM(C50:C52)</f>
+        <v>349545.23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" s="139"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="85"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C55" s="204">
+        <v>1902538.49</v>
+      </c>
+      <c r="D55" s="119" t="s">
+        <v>165</v>
+      </c>
+      <c r="F55" s="116"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C56" s="204">
+        <v>305170.05</v>
+      </c>
+      <c r="D56" s="119" t="s">
+        <v>167</v>
+      </c>
+      <c r="F56" s="116"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="80" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="140">
+        <v>22004.79</v>
+      </c>
+      <c r="D57" s="122" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="80" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" s="140">
+        <v>198043.09</v>
+      </c>
+      <c r="D58" s="122" t="str">
+        <f>D57</f>
+        <v>Debito 12/03</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="80" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C59" s="140">
+        <v>408222.25</v>
+      </c>
+      <c r="D59" s="120" t="str">
+        <f>D58</f>
+        <v>Debito 12/03</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" s="139"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="84">
+        <f>SUM(C55:C59)</f>
+        <v>2835978.67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="139"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="85"/>
+    </row>
+    <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="80" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="80"/>
+      <c r="C62" s="140">
+        <v>598627.16</v>
+      </c>
+      <c r="D62" s="119" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" s="80"/>
+      <c r="C63" s="140">
+        <v>9259.66</v>
+      </c>
+      <c r="D63" s="119" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="80" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="80"/>
+      <c r="C64" s="140">
+        <v>0</v>
+      </c>
+      <c r="D64" s="119"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="169" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" s="170"/>
+      <c r="C65" s="140">
+        <v>204149</v>
+      </c>
+      <c r="D65" s="121" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="167" t="s">
+        <v>172</v>
+      </c>
+      <c r="B66" s="168"/>
+      <c r="C66" s="140">
+        <v>100000</v>
+      </c>
+      <c r="D66" s="121" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="160" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67" s="161"/>
+      <c r="C67" s="140">
+        <v>35200</v>
+      </c>
+      <c r="D67" s="121" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="25"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="84">
+        <f>SUM(C62:C67)</f>
+        <v>947235.82000000007</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B69" s="25"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="87"/>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="167" t="s">
         <v>171</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C48" s="137">
-        <v>1388921.91</v>
-      </c>
-      <c r="D48" s="113"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="137">
-        <v>-302090.52</v>
-      </c>
-      <c r="D49" s="113"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="137">
-        <v>0.61</v>
-      </c>
-      <c r="D50" s="113"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="150"/>
-      <c r="D51" s="113"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="B52" s="112"/>
-      <c r="C52" s="48">
-        <f>SUM(C48:C51)</f>
-        <v>1086832</v>
-      </c>
-      <c r="D52" s="81"/>
-    </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="82">
-        <f>C32+C37+C27+C42+C47+C52</f>
-        <v>6310155.7000000002</v>
-      </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="83"/>
-      <c r="F54" s="14"/>
-    </row>
-    <row r="55" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="205">
-        <v>135000</v>
-      </c>
-      <c r="D55" s="124" t="s">
+      <c r="B70" s="168"/>
+      <c r="C70" s="140">
+        <v>696297</v>
+      </c>
+      <c r="D70" s="119" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="160" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" s="161"/>
+      <c r="C71" s="140">
+        <v>5720</v>
+      </c>
+      <c r="D71" s="121" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+    </row>
+    <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="199" t="s">
         <v>183</v>
       </c>
-      <c r="G55" s="14"/>
-    </row>
-    <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="115" t="s">
-        <v>129</v>
-      </c>
-      <c r="B56" s="107" t="s">
+      <c r="B72" s="158"/>
+      <c r="C72" s="140">
+        <v>250000</v>
+      </c>
+      <c r="D72" s="121" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+    </row>
+    <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="157" t="s">
+        <v>182</v>
+      </c>
+      <c r="B73" s="158"/>
+      <c r="C73" s="140">
+        <v>17983</v>
+      </c>
+      <c r="D73" s="121" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+    </row>
+    <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="167" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" s="168"/>
+      <c r="C74" s="140">
+        <v>103950</v>
+      </c>
+      <c r="D74" s="121" t="s">
+        <v>161</v>
+      </c>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+    </row>
+    <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="167" t="s">
+        <v>158</v>
+      </c>
+      <c r="B75" s="168"/>
+      <c r="C75" s="140">
+        <v>100000</v>
+      </c>
+      <c r="D75" s="121" t="s">
+        <v>180</v>
+      </c>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+    </row>
+    <row r="76" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="167" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="168"/>
+      <c r="C76" s="204">
+        <v>128900</v>
+      </c>
+      <c r="D76" s="121" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="90">
+        <f>SUM(C70:C76)</f>
+        <v>1302850</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" s="141"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="87"/>
+    </row>
+    <row r="79" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="160" t="s">
+        <v>186</v>
+      </c>
+      <c r="B79" s="161"/>
+      <c r="C79" s="140">
+        <f>2*65343</f>
+        <v>130686</v>
+      </c>
+      <c r="D79" s="91"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="80" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="137">
-        <v>211800</v>
-      </c>
-      <c r="D56" s="124" t="s">
+      <c r="B80" s="80"/>
+      <c r="C80" s="140">
+        <f>36414.42+127804.78</f>
+        <v>164219.20000000001</v>
+      </c>
+      <c r="D80" s="89"/>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" s="44"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="84">
+        <f>SUM(C79:C80)</f>
+        <v>294905.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="80"/>
+      <c r="D82" s="93"/>
+    </row>
+    <row r="83" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="164" t="s">
+        <v>139</v>
+      </c>
+      <c r="B83" s="165"/>
+      <c r="C83" s="166"/>
+      <c r="D83" s="94">
+        <f>10000000-9779694.92</f>
+        <v>220305.08000000007</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="C84" s="95"/>
+      <c r="D84" s="96"/>
+      <c r="E84" s="39"/>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" s="10"/>
+      <c r="C85" s="97"/>
+      <c r="D85" s="98">
+        <f>(SUM(D23:D83))</f>
+        <v>10000000</v>
+      </c>
+      <c r="E85" s="39"/>
+      <c r="F85" s="39"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C86" s="95"/>
+      <c r="D86" s="95"/>
+      <c r="F86" s="117"/>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C87" s="95"/>
+      <c r="D87" s="95"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" s="12"/>
+      <c r="C88" s="99"/>
+      <c r="D88" s="100"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="174"/>
+      <c r="B89" s="175"/>
+      <c r="C89" s="88"/>
+      <c r="D89" s="86"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="174"/>
+      <c r="B90" s="175"/>
+      <c r="C90" s="88"/>
+      <c r="D90" s="86"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="103"/>
+      <c r="B91" s="104"/>
+      <c r="C91" s="88"/>
+      <c r="D91" s="86"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="42"/>
+      <c r="B92" s="41"/>
+      <c r="C92" s="49"/>
+      <c r="D92" s="49">
+        <f>SUM(C89:C91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="20"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="124">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B97" s="10"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="58">
+        <f>D92+D95</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="99" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B99" s="79">
+        <f>D85</f>
+        <v>10000000</v>
+      </c>
+      <c r="C99" s="39"/>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" s="79">
+        <f>D85-D83</f>
+        <v>9779694.9199999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="B101" s="79">
+        <f>D97-D95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="B102" s="79">
+        <f>D97</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="173" t="s">
+        <v>159</v>
+      </c>
+      <c r="B105" s="173"/>
+      <c r="C105" s="173"/>
+      <c r="D105" s="173"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="173"/>
+      <c r="B106" s="173"/>
+      <c r="C106" s="173"/>
+      <c r="D106" s="173"/>
+    </row>
+    <row r="107" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="173"/>
+      <c r="B107" s="173"/>
+      <c r="C107" s="173"/>
+      <c r="D107" s="173"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B109" s="35"/>
+    </row>
+    <row r="110" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B110" s="105">
+        <v>7724336.4600000009</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B111" s="36">
+        <f>PRORRATEO!H35</f>
+        <v>12810228.029999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B112" s="89">
+        <f>B126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B113" s="89">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="G56" s="14"/>
-    </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="82">
-        <f>SUM(C55:C56)</f>
-        <v>346800</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="25"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="57"/>
-    </row>
-    <row r="59" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="174" t="s">
-        <v>172</v>
-      </c>
-      <c r="B59" s="175"/>
-      <c r="C59" s="162">
-        <v>10864.97</v>
-      </c>
-      <c r="D59" s="160" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="174" t="s">
-        <v>126</v>
-      </c>
-      <c r="B60" s="175"/>
-      <c r="C60" s="163">
-        <v>4203</v>
-      </c>
-      <c r="D60" s="123"/>
-    </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61" s="25"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="84">
-        <f>SUM(C59:C60)</f>
-        <v>15067.97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B62" s="142"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="85"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="80" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="C63" s="206">
-        <v>1902538.49</v>
-      </c>
-      <c r="D63" s="120" t="s">
-        <v>156</v>
-      </c>
-      <c r="F63" s="116"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="80" t="s">
-        <v>131</v>
-      </c>
-      <c r="B64" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="C64" s="204">
-        <v>22004.79</v>
-      </c>
-      <c r="D64" s="123" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="80" t="s">
-        <v>132</v>
-      </c>
-      <c r="B65" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="C65" s="204">
-        <v>198043.09</v>
-      </c>
-      <c r="D65" s="123" t="str">
-        <f>D64</f>
-        <v>Debito 12/02</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="80" t="s">
-        <v>133</v>
-      </c>
-      <c r="B66" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="C66" s="204">
-        <v>408222.25</v>
-      </c>
-      <c r="D66" s="121" t="str">
-        <f>D65</f>
-        <v>Debito 12/02</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B67" s="142"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="84">
-        <f>SUM(C63:C66)</f>
-        <v>2530808.62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" s="142"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="85"/>
-    </row>
-    <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="80" t="s">
-        <v>134</v>
-      </c>
-      <c r="B69" s="80"/>
-      <c r="C69" s="204">
-        <v>598627.16</v>
-      </c>
-      <c r="D69" s="120" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="B70" s="80"/>
-      <c r="C70" s="143">
-        <v>20460.259999999998</v>
-      </c>
-      <c r="D70" s="120" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="80" t="s">
-        <v>136</v>
-      </c>
-      <c r="B71" s="80"/>
-      <c r="C71" s="143">
-        <v>864000.26</v>
-      </c>
-      <c r="D71" s="120" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="176" t="s">
-        <v>179</v>
-      </c>
-      <c r="B72" s="177"/>
-      <c r="C72" s="143">
-        <v>204149</v>
-      </c>
-      <c r="D72" s="120" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="172" t="s">
-        <v>149</v>
-      </c>
-      <c r="B73" s="173"/>
-      <c r="C73" s="143">
-        <v>0</v>
-      </c>
-      <c r="D73" s="122"/>
-    </row>
-    <row r="74" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="174" t="s">
-        <v>148</v>
-      </c>
-      <c r="B74" s="175"/>
-      <c r="C74" s="143">
-        <v>35200</v>
-      </c>
-      <c r="D74" s="122" t="s">
+      <c r="B114" s="118">
+        <f>-1231-13491-11006-8098</f>
+        <v>-33826</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="17" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="25"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="84">
-        <f>SUM(C69:C74)</f>
-        <v>1722436.6800000002</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B76" s="25"/>
-      <c r="C76" s="30"/>
-      <c r="D76" s="87"/>
-    </row>
-    <row r="77" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="145" t="s">
-        <v>165</v>
-      </c>
-      <c r="B77" s="144"/>
-      <c r="C77" s="143">
-        <v>51919.14</v>
-      </c>
-      <c r="D77" s="118" t="s">
+      <c r="B115" s="118">
+        <v>-240000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="17" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="208" t="s">
-        <v>184</v>
-      </c>
-      <c r="B78" s="209"/>
-      <c r="C78" s="207"/>
-      <c r="D78" s="120" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="149" t="s">
-        <v>158</v>
-      </c>
-      <c r="B79" s="141"/>
-      <c r="C79" s="143">
-        <v>10000</v>
-      </c>
-      <c r="D79" s="140" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="149" t="s">
-        <v>167</v>
-      </c>
-      <c r="B80" s="141"/>
-      <c r="C80" s="143">
-        <v>8760.52</v>
-      </c>
-      <c r="D80" s="122" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="174" t="s">
-        <v>182</v>
-      </c>
-      <c r="B81" s="175"/>
-      <c r="C81" s="204">
-        <v>5720</v>
-      </c>
-      <c r="D81" s="122" t="s">
-        <v>166</v>
-      </c>
-      <c r="E81" s="39"/>
-      <c r="F81" s="39"/>
-    </row>
-    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="172" t="s">
-        <v>180</v>
-      </c>
-      <c r="B82" s="173"/>
-      <c r="C82" s="204">
-        <v>103950</v>
-      </c>
-      <c r="D82" s="122" t="s">
-        <v>183</v>
-      </c>
-      <c r="E82" s="39"/>
-      <c r="F82" s="39"/>
-    </row>
-    <row r="83" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="172" t="s">
-        <v>180</v>
-      </c>
-      <c r="B83" s="173"/>
-      <c r="C83" s="206">
-        <v>128900</v>
-      </c>
-      <c r="D83" s="122" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="25" t="s">
+      <c r="B116" s="118">
+        <v>-260000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B117" s="118">
+        <f>-B100</f>
+        <v>-9779694.9199999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B118" s="89">
+        <f>-(B101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B84" s="24"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="90">
-        <f>SUM(C77:C83)</f>
-        <v>309249.66000000003</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B85" s="146"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="87"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="B86" s="80"/>
-      <c r="C86" s="143">
-        <v>65343</v>
-      </c>
-      <c r="D86" s="91"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="80" t="s">
-        <v>125</v>
-      </c>
-      <c r="B87" s="80"/>
-      <c r="C87" s="143">
-        <f>65.19+149249.14</f>
-        <v>149314.33000000002</v>
-      </c>
-      <c r="D87" s="89"/>
-    </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B88" s="44"/>
-      <c r="C88" s="92"/>
-      <c r="D88" s="84">
-        <f>SUM(C86:C87)</f>
-        <v>214657.33000000002</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="80"/>
-      <c r="D89" s="93"/>
-    </row>
-    <row r="90" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="169" t="s">
-        <v>141</v>
-      </c>
-      <c r="B90" s="170"/>
-      <c r="C90" s="171"/>
-      <c r="D90" s="94">
-        <f>10000000-8703429.85</f>
-        <v>1296570.1500000004</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="1"/>
-      <c r="C91" s="95"/>
-      <c r="D91" s="96"/>
-      <c r="E91" s="39"/>
-    </row>
-    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B92" s="10"/>
-      <c r="C92" s="97"/>
-      <c r="D92" s="98">
-        <f>(SUM(D33:D90))</f>
-        <v>12745746.109999999</v>
-      </c>
-      <c r="E92" s="39"/>
-      <c r="F92" s="39"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C93" s="95"/>
-      <c r="D93" s="95"/>
-      <c r="F93" s="117"/>
-    </row>
-    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="95"/>
-      <c r="D94" s="95"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B95" s="12"/>
-      <c r="C95" s="99"/>
-      <c r="D95" s="100"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="167"/>
-      <c r="B96" s="168"/>
-      <c r="C96" s="88"/>
-      <c r="D96" s="86"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="167"/>
-      <c r="B97" s="168"/>
-      <c r="C97" s="88"/>
-      <c r="D97" s="86"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="103"/>
-      <c r="B98" s="104"/>
-      <c r="C98" s="88"/>
-      <c r="D98" s="86"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="42"/>
-      <c r="B99" s="41"/>
-      <c r="C99" s="49"/>
-      <c r="D99" s="49">
-        <f>SUM(C96:C98)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B102" s="20"/>
-      <c r="C102" s="21"/>
-      <c r="D102" s="125">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="104" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B104" s="10"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="58">
-        <f>D99+D102</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="106" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="78" t="s">
-        <v>31</v>
-      </c>
-      <c r="B106" s="79">
-        <f>D92</f>
-        <v>12745746.109999999</v>
-      </c>
-      <c r="C106" s="39"/>
-    </row>
-    <row r="107" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="78" t="s">
-        <v>32</v>
-      </c>
-      <c r="B107" s="79">
-        <f>D92-D90</f>
-        <v>11449175.959999999</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="B108" s="79">
-        <f>D104-D102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="78" t="s">
-        <v>88</v>
-      </c>
-      <c r="B109" s="79">
-        <f>D104</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="166" t="s">
-        <v>181</v>
-      </c>
-      <c r="B112" s="166"/>
-      <c r="C112" s="166"/>
-      <c r="D112" s="166"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="166"/>
-      <c r="B113" s="166"/>
-      <c r="C113" s="166"/>
-      <c r="D113" s="166"/>
-    </row>
-    <row r="114" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="166"/>
-      <c r="B114" s="166"/>
-      <c r="C114" s="166"/>
-      <c r="D114" s="166"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B116" s="35"/>
-    </row>
-    <row r="117" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B117" s="105">
-        <v>7139335.7599999998</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B118" s="36">
-        <f>PRORRATEO!H35</f>
-        <v>12003298.140000001</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B119" s="89">
-        <f>B132</f>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="B120" s="119">
-        <v>-10167</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="B121" s="119">
-        <v>-240000</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="B122" s="119">
-        <v>-260000</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="B123" s="119">
-        <f>-B107</f>
-        <v>-11449175.959999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B124" s="89">
-        <f>-(B108)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="22" t="s">
+      <c r="B119" s="105">
+        <f>SUM(B110:B118)</f>
+        <v>10621043.570000002</v>
+      </c>
+      <c r="D119" s="201"/>
+    </row>
+    <row r="120" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="37"/>
+      <c r="C120" s="39"/>
+      <c r="E120" s="203"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D121" s="202"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" s="172" t="s">
+        <v>78</v>
+      </c>
+      <c r="B122" s="172"/>
+    </row>
+    <row r="123" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="172"/>
+      <c r="B123" s="172"/>
+    </row>
+    <row r="124" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="101"/>
+      <c r="B124" s="29"/>
+    </row>
+    <row r="125" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="101"/>
+      <c r="B125" s="29"/>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B125" s="105">
-        <f>SUM(B117:B124)</f>
-        <v>7683290.9399999995</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="37"/>
-      <c r="C126" s="39"/>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="165" t="s">
-        <v>78</v>
-      </c>
-      <c r="B128" s="165"/>
-    </row>
-    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="165"/>
-      <c r="B129" s="165"/>
-    </row>
-    <row r="130" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="101" t="s">
-        <v>152</v>
-      </c>
-      <c r="B130" s="29">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="101" t="s">
-        <v>152</v>
-      </c>
-      <c r="B131" s="29">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B132" s="102">
-        <f>SUM(B130:B131)</f>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L133" s="8"/>
-    </row>
-    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="164"/>
-      <c r="B134" s="164"/>
-      <c r="C134" s="164"/>
-      <c r="D134" s="164"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="164"/>
-      <c r="B135" s="164"/>
-      <c r="C135" s="164"/>
-      <c r="D135" s="164"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="164"/>
-      <c r="B136" s="164"/>
-      <c r="C136" s="164"/>
-      <c r="D136" s="164"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="164"/>
-      <c r="B137" s="164"/>
-      <c r="C137" s="164"/>
-      <c r="D137" s="164"/>
+      <c r="B126" s="102">
+        <f>SUM(B124:B125)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L127" s="8"/>
+    </row>
+    <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="171"/>
+      <c r="B128" s="171"/>
+      <c r="C128" s="171"/>
+      <c r="D128" s="171"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="171"/>
+      <c r="B129" s="171"/>
+      <c r="C129" s="171"/>
+      <c r="D129" s="171"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="171"/>
+      <c r="B130" s="171"/>
+      <c r="C130" s="171"/>
+      <c r="D130" s="171"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="171"/>
+      <c r="B131" s="171"/>
+      <c r="C131" s="171"/>
+      <c r="D131" s="171"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="F32:G32"/>
+  <mergeCells count="21">
+    <mergeCell ref="A128:D131"/>
+    <mergeCell ref="A122:B123"/>
+    <mergeCell ref="A105:D107"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A79:B79"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A134:D137"/>
-    <mergeCell ref="A128:B129"/>
-    <mergeCell ref="A112:D114"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A51:B51"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3147,32 +3097,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="189" t="str">
+      <c r="B1" s="176" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco Santander
 Tipo de cuenta: Cuenta corriente en pesos
@@ -3180,139 +3130,139 @@
 CBU: 0720039720000002345040
 Alias: ALFA.CETRO.AMOROSAS</v>
       </c>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="189"/>
-      <c r="I1" s="189"/>
-      <c r="J1" s="189"/>
-      <c r="K1" s="189"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="189"/>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="189"/>
-      <c r="F2" s="189"/>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
-      <c r="K2" s="189"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="138">
+      <c r="O2" s="137">
         <v>10000000</v>
       </c>
       <c r="P2" s="46"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="190"/>
-      <c r="K3" s="190"/>
+      <c r="B3" s="177"/>
+      <c r="C3" s="177"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="177"/>
+      <c r="K3" s="177"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="139">
+      <c r="O3" s="138">
         <v>2000000</v>
       </c>
       <c r="P3" s="50"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="183" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="185" t="s">
+      <c r="B4" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="187" t="s">
+      <c r="C4" s="180" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="187" t="s">
+      <c r="D4" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="187" t="s">
+      <c r="E4" s="180" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="187" t="s">
+      <c r="F4" s="180" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="187" t="s">
+      <c r="G4" s="180" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="187" t="s">
+      <c r="H4" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="187" t="s">
+      <c r="I4" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="196" t="s">
+      <c r="J4" s="185" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="194" t="s">
+      <c r="K4" s="182" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="194" t="s">
+      <c r="L4" s="182" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="194" t="s">
+      <c r="M4" s="182" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="199" t="s">
+      <c r="N4" s="188" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="191" t="s">
+      <c r="P4" s="178" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="184"/>
-      <c r="B5" s="186"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="193"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="193"/>
-      <c r="J5" s="197"/>
-      <c r="K5" s="195"/>
-      <c r="L5" s="198"/>
-      <c r="M5" s="195"/>
-      <c r="N5" s="200"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="194"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="183"/>
+      <c r="L5" s="187"/>
+      <c r="M5" s="183"/>
+      <c r="N5" s="189"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="P5" s="192"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="179"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3330,11 +3280,11 @@
         <v>4.57</v>
       </c>
       <c r="G6" s="60">
-        <v>502700.01</v>
+        <v>548400.01</v>
       </c>
       <c r="H6" s="61">
         <f>G6</f>
-        <v>502700.01</v>
+        <v>548400.01</v>
       </c>
       <c r="I6" s="62"/>
       <c r="J6" s="63">
@@ -3368,55 +3318,55 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="151">
+      <c r="B7" s="144">
         <v>2</v>
       </c>
-      <c r="C7" s="151" t="s">
+      <c r="C7" s="144" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="151" t="s">
+      <c r="D7" s="144" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="158"/>
-      <c r="F7" s="152">
+      <c r="E7" s="151"/>
+      <c r="F7" s="145">
         <v>3.07</v>
       </c>
       <c r="G7" s="61">
-        <v>347831.02</v>
+        <v>379452.02</v>
       </c>
       <c r="H7" s="61">
         <f>G7</f>
-        <v>347831.02</v>
+        <v>379452.02</v>
       </c>
       <c r="I7" s="62"/>
-      <c r="J7" s="153">
+      <c r="J7" s="146">
         <f t="shared" ref="J7:J32" si="2">G7-H7</f>
         <v>0</v>
       </c>
-      <c r="K7" s="153">
+      <c r="K7" s="146">
         <f t="shared" ref="K7:K33" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="154">
+      <c r="L7" s="147">
         <f t="shared" ref="L7:L34" si="4">O$3*F7%</f>
         <v>61399.999999999993</v>
       </c>
-      <c r="M7" s="154">
+      <c r="M7" s="147">
         <f t="shared" ref="M7:M34" si="5">O$2*F7%</f>
         <v>307000</v>
       </c>
-      <c r="N7" s="155">
-        <v>0</v>
-      </c>
-      <c r="O7" s="156">
+      <c r="N7" s="148">
+        <v>0</v>
+      </c>
+      <c r="O7" s="149">
         <f t="shared" si="0"/>
         <v>368400.02</v>
       </c>
-      <c r="P7" s="157">
+      <c r="P7" s="150">
         <f t="shared" si="1"/>
         <v>379452.02</v>
       </c>
@@ -3425,91 +3375,89 @@
         <v>0.02</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="126">
+      <c r="B8" s="125">
         <v>3</v>
       </c>
-      <c r="C8" s="126" t="s">
+      <c r="C8" s="125" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="127" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" s="128"/>
-      <c r="F8" s="129">
+      <c r="D8" s="126" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="127"/>
+      <c r="F8" s="128">
         <v>4.55</v>
       </c>
-      <c r="G8" s="130">
-        <v>1015765.03</v>
-      </c>
-      <c r="H8" s="130">
-        <v>505000</v>
-      </c>
-      <c r="I8" s="131"/>
-      <c r="J8" s="132">
+      <c r="G8" s="129">
+        <v>1071833.03</v>
+      </c>
+      <c r="H8" s="129">
+        <v>510765</v>
+      </c>
+      <c r="I8" s="130"/>
+      <c r="J8" s="131">
         <f t="shared" si="2"/>
-        <v>510765.03</v>
-      </c>
-      <c r="K8" s="132">
+        <v>561068.03</v>
+      </c>
+      <c r="K8" s="131">
         <f t="shared" si="3"/>
-        <v>15067.568385000002</v>
-      </c>
-      <c r="L8" s="133">
+        <v>16551.506885000003</v>
+      </c>
+      <c r="L8" s="132">
         <f t="shared" si="4"/>
         <v>91000</v>
       </c>
-      <c r="M8" s="133">
+      <c r="M8" s="132">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N8" s="134">
-        <v>0</v>
-      </c>
-      <c r="O8" s="135">
+      <c r="N8" s="133">
+        <v>0</v>
+      </c>
+      <c r="O8" s="134">
         <f t="shared" si="0"/>
-        <v>1071833.03</v>
-      </c>
-      <c r="P8" s="136">
+        <v>1123620.03</v>
+      </c>
+      <c r="P8" s="135">
         <f t="shared" si="1"/>
-        <v>1103988.03</v>
+        <v>1157329.03</v>
       </c>
       <c r="Q8" s="39">
         <f t="shared" ref="Q8:Q33" si="6">Q7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="201" t="s">
-        <v>174</v>
-      </c>
-      <c r="C9" s="202"/>
-      <c r="D9" s="203"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="130">
-        <v>400000</v>
-      </c>
-      <c r="H9" s="130">
-        <v>400000</v>
-      </c>
-      <c r="I9" s="131"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="133"/>
-      <c r="M9" s="133"/>
-      <c r="N9" s="134"/>
-      <c r="O9" s="135"/>
-      <c r="P9" s="136"/>
+      <c r="B9" s="190" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="191"/>
+      <c r="D9" s="192"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129">
+        <v>0</v>
+      </c>
+      <c r="I9" s="130"/>
+      <c r="J9" s="131"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="132"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="134"/>
+      <c r="P9" s="135"/>
       <c r="Q9" s="39"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3527,15 +3475,15 @@
         <v>3.05</v>
       </c>
       <c r="G10" s="60">
-        <v>323930.03999999998</v>
+        <v>350128.04</v>
       </c>
       <c r="H10" s="61">
-        <v>350000</v>
+        <v>360000</v>
       </c>
       <c r="I10" s="62"/>
       <c r="J10" s="63">
         <f t="shared" si="2"/>
-        <v>-26069.960000000021</v>
+        <v>-9871.960000000021</v>
       </c>
       <c r="K10" s="63">
         <f t="shared" si="3"/>
@@ -3554,22 +3502,22 @@
       </c>
       <c r="O10" s="66">
         <f t="shared" si="0"/>
-        <v>339930.04</v>
+        <v>356128.04</v>
       </c>
       <c r="P10" s="67">
         <f t="shared" si="1"/>
-        <v>350128.04</v>
+        <v>366812.04</v>
       </c>
       <c r="Q10" s="39">
         <f>Q8+0.01</f>
         <v>0.04</v>
       </c>
       <c r="R10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S10" s="39"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -3587,17 +3535,20 @@
         <v>4.55</v>
       </c>
       <c r="G11" s="60">
-        <v>515626.05</v>
-      </c>
-      <c r="H11" s="61"/>
+        <v>1076837.05</v>
+      </c>
+      <c r="H11" s="61">
+        <f>1080000</f>
+        <v>1080000</v>
+      </c>
       <c r="I11" s="62"/>
       <c r="J11" s="63">
         <f t="shared" si="2"/>
-        <v>515626.05</v>
+        <v>-3162.9499999999534</v>
       </c>
       <c r="K11" s="63">
         <f t="shared" si="3"/>
-        <v>15210.968475000001</v>
+        <v>0</v>
       </c>
       <c r="L11" s="64">
         <f t="shared" si="4"/>
@@ -3612,11 +3563,11 @@
       </c>
       <c r="O11" s="66">
         <f t="shared" si="0"/>
-        <v>1076837.05</v>
+        <v>542837.05000000005</v>
       </c>
       <c r="P11" s="67">
         <f t="shared" si="1"/>
-        <v>1109142.05</v>
+        <v>559122.05000000005</v>
       </c>
       <c r="Q11" s="39">
         <f t="shared" si="6"/>
@@ -3624,7 +3575,7 @@
       </c>
       <c r="S11" s="39"/>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -3642,16 +3593,15 @@
         <v>3.05</v>
       </c>
       <c r="G12" s="60">
-        <v>335500.06</v>
+        <v>366000.06</v>
       </c>
       <c r="H12" s="61">
-        <f>G12</f>
-        <v>335500.06</v>
+        <v>376980.06</v>
       </c>
       <c r="I12" s="62"/>
       <c r="J12" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10980</v>
       </c>
       <c r="K12" s="63">
         <f t="shared" si="3"/>
@@ -3670,66 +3620,66 @@
       </c>
       <c r="O12" s="66">
         <f t="shared" si="0"/>
-        <v>366000.06</v>
+        <v>355020.06</v>
       </c>
       <c r="P12" s="67">
         <f t="shared" si="1"/>
-        <v>376980.06</v>
+        <v>365671.06</v>
       </c>
       <c r="Q12" s="39">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="151">
+      <c r="B13" s="144">
         <v>7</v>
       </c>
-      <c r="C13" s="151" t="s">
+      <c r="C13" s="144" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="151" t="s">
+      <c r="D13" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="151"/>
-      <c r="F13" s="152">
+      <c r="E13" s="144"/>
+      <c r="F13" s="145">
         <v>4.55</v>
       </c>
       <c r="G13" s="61">
-        <v>1011647.07</v>
+        <v>546000.06999999995</v>
       </c>
       <c r="H13" s="61">
-        <f>240000+260000+501000+10647</f>
-        <v>1011647</v>
+        <f>G13</f>
+        <v>546000.06999999995</v>
       </c>
       <c r="I13" s="62"/>
-      <c r="J13" s="153">
+      <c r="J13" s="146">
         <f t="shared" si="2"/>
-        <v>6.9999999948777258E-2</v>
-      </c>
-      <c r="K13" s="153">
+        <v>0</v>
+      </c>
+      <c r="K13" s="146">
         <f t="shared" si="3"/>
-        <v>2.0649999984889292E-3</v>
-      </c>
-      <c r="L13" s="154">
+        <v>0</v>
+      </c>
+      <c r="L13" s="147">
         <f t="shared" si="4"/>
         <v>91000</v>
       </c>
-      <c r="M13" s="154">
+      <c r="M13" s="147">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N13" s="155">
-        <v>0</v>
-      </c>
-      <c r="O13" s="156">
+      <c r="N13" s="148">
+        <v>0</v>
+      </c>
+      <c r="O13" s="149">
         <f t="shared" si="0"/>
         <v>546000.06999999995</v>
       </c>
-      <c r="P13" s="157">
+      <c r="P13" s="150">
         <f t="shared" si="1"/>
         <v>562380.06999999995</v>
       </c>
@@ -3740,7 +3690,7 @@
       <c r="R13" s="117"/>
       <c r="S13" s="116"/>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3758,15 +3708,16 @@
         <v>3.05</v>
       </c>
       <c r="G14" s="60">
-        <v>325702.08</v>
+        <v>356229.08</v>
       </c>
       <c r="H14" s="61">
-        <v>335473</v>
+        <f>G14</f>
+        <v>356229.08</v>
       </c>
       <c r="I14" s="62"/>
       <c r="J14" s="63">
         <f t="shared" si="2"/>
-        <v>-9770.9199999999837</v>
+        <v>0</v>
       </c>
       <c r="K14" s="63">
         <f t="shared" si="3"/>
@@ -3785,18 +3736,18 @@
       </c>
       <c r="O14" s="66">
         <f t="shared" si="0"/>
-        <v>356229.08</v>
+        <v>366000.08</v>
       </c>
       <c r="P14" s="67">
         <f t="shared" si="1"/>
-        <v>366916.08</v>
+        <v>376980.08</v>
       </c>
       <c r="Q14" s="39">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
@@ -3814,19 +3765,19 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="G15" s="60">
-        <v>498800.09</v>
-      </c>
-      <c r="H15" s="161">
-        <v>514000</v>
+        <v>532000.09</v>
+      </c>
+      <c r="H15" s="154">
+        <v>532000</v>
       </c>
       <c r="I15" s="62"/>
       <c r="J15" s="63">
         <f t="shared" si="2"/>
-        <v>-15199.909999999974</v>
+        <v>8.999999996740371E-2</v>
       </c>
       <c r="K15" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.6549999990384096E-3</v>
       </c>
       <c r="L15" s="64">
         <f t="shared" si="4"/>
@@ -3841,21 +3792,21 @@
       </c>
       <c r="O15" s="66">
         <f t="shared" si="0"/>
-        <v>532000.09</v>
+        <v>547200.09</v>
       </c>
       <c r="P15" s="67">
         <f t="shared" si="1"/>
-        <v>547960.09</v>
+        <v>563616.09</v>
       </c>
       <c r="Q15" s="39">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
       <c r="R15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3873,20 +3824,19 @@
         <v>3.05</v>
       </c>
       <c r="G16" s="60">
-        <v>335500.09999999998</v>
+        <v>366000.1</v>
       </c>
       <c r="H16" s="61">
-        <f>G16</f>
-        <v>335500.09999999998</v>
+        <v>365000</v>
       </c>
       <c r="I16" s="62"/>
       <c r="J16" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1000.0999999999767</v>
       </c>
       <c r="K16" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29.502949999999316</v>
       </c>
       <c r="L16" s="64">
         <f t="shared" si="4"/>
@@ -3901,21 +3851,21 @@
       </c>
       <c r="O16" s="66">
         <f t="shared" si="0"/>
-        <v>366000.1</v>
+        <v>367030.1</v>
       </c>
       <c r="P16" s="67">
         <f t="shared" si="1"/>
-        <v>376980.1</v>
+        <v>378041.1</v>
       </c>
       <c r="Q16" s="39">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R16" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -3933,11 +3883,11 @@
         <v>4.55</v>
       </c>
       <c r="G17" s="60">
-        <v>485485.11</v>
+        <v>546000.11</v>
       </c>
       <c r="H17" s="61">
         <f>G17</f>
-        <v>485485.11</v>
+        <v>546000.11</v>
       </c>
       <c r="I17" s="62"/>
       <c r="J17" s="63">
@@ -3972,7 +3922,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3990,20 +3940,20 @@
         <v>3.05</v>
       </c>
       <c r="G18" s="60">
-        <v>762336.12</v>
+        <v>836828.12</v>
       </c>
       <c r="H18" s="61">
-        <f>300000+5000</f>
-        <v>305000</v>
+        <f>G18</f>
+        <v>836828.12</v>
       </c>
       <c r="I18" s="62"/>
       <c r="J18" s="63">
         <f t="shared" si="2"/>
-        <v>457336.12</v>
+        <v>0</v>
       </c>
       <c r="K18" s="63">
         <f t="shared" si="3"/>
-        <v>13491.41554</v>
+        <v>0</v>
       </c>
       <c r="L18" s="64">
         <f t="shared" si="4"/>
@@ -4018,18 +3968,18 @@
       </c>
       <c r="O18" s="66">
         <f t="shared" si="0"/>
-        <v>836828.12</v>
+        <v>366000.12</v>
       </c>
       <c r="P18" s="67">
         <f t="shared" si="1"/>
-        <v>861933.12</v>
+        <v>376980.12</v>
       </c>
       <c r="Q18" s="39">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -4047,16 +3997,15 @@
         <v>4.55</v>
       </c>
       <c r="G19" s="60">
-        <v>500500.13</v>
+        <v>546000.13</v>
       </c>
       <c r="H19" s="61">
-        <f>G19</f>
-        <v>500500.13</v>
+        <v>562380.13</v>
       </c>
       <c r="I19" s="62"/>
       <c r="J19" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-16380</v>
       </c>
       <c r="K19" s="63">
         <f t="shared" si="3"/>
@@ -4075,18 +4024,18 @@
       </c>
       <c r="O19" s="66">
         <f t="shared" si="0"/>
-        <v>546000.13</v>
+        <v>529620.13</v>
       </c>
       <c r="P19" s="67">
         <f t="shared" si="1"/>
-        <v>562380.13</v>
+        <v>545509.13</v>
       </c>
       <c r="Q19" s="39">
         <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -4104,11 +4053,11 @@
         <v>3.18</v>
       </c>
       <c r="G20" s="60">
-        <v>349800.14</v>
+        <v>381600.14</v>
       </c>
       <c r="H20" s="61">
         <f>G20</f>
-        <v>349800.14</v>
+        <v>381600.14</v>
       </c>
       <c r="I20" s="62"/>
       <c r="J20" s="63">
@@ -4143,7 +4092,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
@@ -4161,11 +4110,11 @@
         <v>4.55</v>
       </c>
       <c r="G21" s="60">
-        <v>500500.15</v>
+        <v>546000.15</v>
       </c>
       <c r="H21" s="61">
         <f>G21</f>
-        <v>500500.15</v>
+        <v>546000.15</v>
       </c>
       <c r="I21" s="62"/>
       <c r="J21" s="63">
@@ -4200,7 +4149,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4218,15 +4167,16 @@
         <v>3.17</v>
       </c>
       <c r="G22" s="60">
-        <v>348154.16</v>
+        <v>378554.16</v>
       </c>
       <c r="H22" s="61">
-        <v>350000</v>
+        <f>G22</f>
+        <v>378554.16</v>
       </c>
       <c r="I22" s="62"/>
       <c r="J22" s="63">
         <f t="shared" si="2"/>
-        <v>-1845.8400000000256</v>
+        <v>0</v>
       </c>
       <c r="K22" s="63">
         <f t="shared" si="3"/>
@@ -4245,22 +4195,22 @@
       </c>
       <c r="O22" s="66">
         <f t="shared" si="0"/>
-        <v>378554.16</v>
+        <v>380400.16</v>
       </c>
       <c r="P22" s="67">
         <f t="shared" si="1"/>
-        <v>389911.16</v>
+        <v>391812.16</v>
       </c>
       <c r="Q22" s="39">
         <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
       <c r="R22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="S22" s="38"/>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>20</v>
       </c>
@@ -4278,16 +4228,16 @@
         <v>4.55</v>
       </c>
       <c r="G23" s="61">
-        <v>1015765.17</v>
+        <v>515527.17</v>
       </c>
       <c r="H23" s="61">
-        <f>1046238.17</f>
-        <v>1046238.17</v>
+        <f>G23</f>
+        <v>515527.17</v>
       </c>
       <c r="I23" s="62"/>
       <c r="J23" s="63">
         <f t="shared" si="2"/>
-        <v>-30473</v>
+        <v>0</v>
       </c>
       <c r="K23" s="63">
         <f t="shared" si="3"/>
@@ -4306,18 +4256,18 @@
       </c>
       <c r="O23" s="66">
         <f t="shared" si="0"/>
-        <v>515527.17</v>
+        <v>546000.17000000004</v>
       </c>
       <c r="P23" s="67">
         <f t="shared" si="1"/>
-        <v>530993.16999999993</v>
+        <v>562380.17000000004</v>
       </c>
       <c r="Q23" s="39">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4335,16 +4285,15 @@
         <v>3.17</v>
       </c>
       <c r="G24" s="60">
-        <v>348700.18</v>
+        <v>380400.18</v>
       </c>
       <c r="H24" s="61">
-        <f>G24</f>
-        <v>348700.18</v>
+        <v>391812.18</v>
       </c>
       <c r="I24" s="62"/>
       <c r="J24" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-11412</v>
       </c>
       <c r="K24" s="63">
         <f t="shared" si="3"/>
@@ -4363,18 +4312,18 @@
       </c>
       <c r="O24" s="66">
         <f t="shared" si="0"/>
-        <v>380400.18</v>
+        <v>368988.18</v>
       </c>
       <c r="P24" s="67">
         <f t="shared" si="1"/>
-        <v>391812.18</v>
+        <v>380058.18</v>
       </c>
       <c r="Q24" s="39">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
@@ -4392,11 +4341,11 @@
         <v>4.55</v>
       </c>
       <c r="G25" s="60">
-        <v>500500.19</v>
+        <v>546000.18999999994</v>
       </c>
       <c r="H25" s="61">
         <f>G25</f>
-        <v>500500.19</v>
+        <v>546000.18999999994</v>
       </c>
       <c r="I25" s="62"/>
       <c r="J25" s="63">
@@ -4431,7 +4380,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
@@ -4449,11 +4398,11 @@
         <v>3.17</v>
       </c>
       <c r="G26" s="61">
-        <v>348700.2</v>
+        <v>380400.2</v>
       </c>
       <c r="H26" s="61">
         <f>G26</f>
-        <v>348700.2</v>
+        <v>380400.2</v>
       </c>
       <c r="I26" s="62"/>
       <c r="J26" s="63">
@@ -4488,10 +4437,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="S26" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
@@ -4509,11 +4458,11 @@
         <v>4.55</v>
       </c>
       <c r="G27" s="60">
-        <v>500500.21</v>
+        <v>546000.21</v>
       </c>
       <c r="H27" s="61">
         <f>G27</f>
-        <v>500500.21</v>
+        <v>546000.21</v>
       </c>
       <c r="I27" s="62"/>
       <c r="J27" s="63">
@@ -4548,7 +4497,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
@@ -4566,16 +4515,15 @@
         <v>3.17</v>
       </c>
       <c r="G28" s="60">
-        <v>-168789.78</v>
+        <v>-170259.78</v>
       </c>
       <c r="H28" s="61">
-        <f>381870.22</f>
-        <v>381870.22</v>
+        <v>175367.78</v>
       </c>
       <c r="I28" s="62"/>
       <c r="J28" s="63">
         <f t="shared" si="2"/>
-        <v>-550660</v>
+        <v>-345627.56</v>
       </c>
       <c r="K28" s="63">
         <f t="shared" si="3"/>
@@ -4594,18 +4542,18 @@
       </c>
       <c r="O28" s="66">
         <f t="shared" si="0"/>
-        <v>-170259.78</v>
+        <v>34772.22</v>
       </c>
       <c r="P28" s="67">
         <f t="shared" si="1"/>
-        <v>-175367.78</v>
+        <v>35815.22</v>
       </c>
       <c r="Q28" s="39">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
@@ -4623,11 +4571,11 @@
         <v>4.66</v>
       </c>
       <c r="G29" s="60">
-        <v>512600.23</v>
+        <v>559200.23</v>
       </c>
       <c r="H29" s="61">
         <f>G29</f>
-        <v>512600.23</v>
+        <v>559200.23</v>
       </c>
       <c r="I29" s="62"/>
       <c r="J29" s="63">
@@ -4662,7 +4610,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4680,11 +4628,11 @@
         <v>3.21</v>
       </c>
       <c r="G30" s="60">
-        <v>353100.24</v>
+        <v>385200.24</v>
       </c>
       <c r="H30" s="61">
         <f>G30</f>
-        <v>353100.24</v>
+        <v>385200.24</v>
       </c>
       <c r="I30" s="62"/>
       <c r="J30" s="63">
@@ -4719,7 +4667,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4737,16 +4685,15 @@
         <v>4.6900000000000004</v>
       </c>
       <c r="G31" s="60">
-        <v>500423.25</v>
+        <v>562800.25</v>
       </c>
       <c r="H31" s="61">
-        <f>G31</f>
-        <v>500423.25</v>
+        <v>579684.25</v>
       </c>
       <c r="I31" s="62"/>
       <c r="J31" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-16884</v>
       </c>
       <c r="K31" s="63">
         <f t="shared" si="3"/>
@@ -4765,21 +4712,21 @@
       </c>
       <c r="O31" s="66">
         <f t="shared" si="0"/>
-        <v>562800.25</v>
+        <v>545916.25</v>
       </c>
       <c r="P31" s="67">
         <f t="shared" si="1"/>
-        <v>579684.25</v>
+        <v>562293.25</v>
       </c>
       <c r="Q31" s="39">
         <f t="shared" si="6"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="R31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4797,16 +4744,15 @@
         <v>3.02</v>
       </c>
       <c r="G32" s="60">
-        <v>363600.26</v>
+        <v>393800.26</v>
       </c>
       <c r="H32" s="61">
-        <f>G32</f>
-        <v>363600.26</v>
+        <v>405614.26</v>
       </c>
       <c r="I32" s="62"/>
       <c r="J32" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-11814</v>
       </c>
       <c r="K32" s="63">
         <f t="shared" si="3"/>
@@ -4825,11 +4771,11 @@
       </c>
       <c r="O32" s="66">
         <f t="shared" si="0"/>
-        <v>393800.26</v>
+        <v>381986.26</v>
       </c>
       <c r="P32" s="67">
         <f t="shared" si="1"/>
-        <v>405614.26</v>
+        <v>393446.26</v>
       </c>
       <c r="Q32" s="111">
         <f t="shared" si="6"/>
@@ -4837,10 +4783,10 @@
       </c>
       <c r="R32" s="116"/>
       <c r="S32" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4858,15 +4804,15 @@
         <v>0.16</v>
       </c>
       <c r="G33" s="60">
-        <v>17600.27</v>
+        <v>18672.27</v>
       </c>
       <c r="H33" s="61">
-        <v>18128.27</v>
+        <v>19232.27</v>
       </c>
       <c r="I33" s="62"/>
       <c r="J33" s="63">
         <f>G33-H33</f>
-        <v>-528</v>
+        <v>-560</v>
       </c>
       <c r="K33" s="63">
         <f t="shared" si="3"/>
@@ -4885,18 +4831,18 @@
       </c>
       <c r="O33" s="66">
         <f t="shared" si="0"/>
-        <v>18672.27</v>
+        <v>18640.27</v>
       </c>
       <c r="P33" s="67">
         <f t="shared" si="1"/>
-        <v>19232.27</v>
+        <v>19199.27</v>
       </c>
       <c r="Q33" s="39">
         <f t="shared" si="6"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>27</v>
       </c>
@@ -4942,7 +4888,7 @@
       </c>
       <c r="Q34" s="39"/>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="73"/>
       <c r="C35" s="74"/>
       <c r="D35" s="75"/>
@@ -4953,11 +4899,11 @@
       </c>
       <c r="G35" s="45">
         <f>SUM(G6:G34)</f>
-        <v>12852477.779999999</v>
+        <v>12945603.779999999</v>
       </c>
       <c r="H35" s="52">
         <f>SUM(H6:H34)</f>
-        <v>12003298.140000001</v>
+        <v>12810228.029999999</v>
       </c>
       <c r="I35" s="52">
         <f t="shared" ref="I35" si="10">SUM(I6:I34)</f>
@@ -4979,106 +4925,111 @@
       </c>
       <c r="O35" s="77">
         <f>SUM(O6:O33)</f>
-        <v>12924353.779999999</v>
+        <v>12183360.779999999</v>
       </c>
       <c r="P35" s="77">
         <f>SUM(P6:P33)</f>
-        <v>13312084.779999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>12548862.779999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="43"/>
       <c r="E36" s="43"/>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="164" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" s="164"/>
-      <c r="F38" s="164"/>
-      <c r="G38" s="164"/>
-      <c r="H38" s="164"/>
-      <c r="I38" s="164"/>
-      <c r="J38" s="164"/>
-      <c r="K38" s="164"/>
-      <c r="L38" s="164"/>
-      <c r="M38" s="164"/>
-      <c r="N38" s="164"/>
-      <c r="O38" s="164"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="164"/>
-      <c r="E39" s="164"/>
-      <c r="F39" s="164"/>
-      <c r="G39" s="164"/>
-      <c r="H39" s="164"/>
-      <c r="I39" s="164"/>
-      <c r="J39" s="164"/>
-      <c r="K39" s="164"/>
-      <c r="L39" s="164"/>
-      <c r="M39" s="164"/>
-      <c r="N39" s="164"/>
-      <c r="O39" s="164"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="164"/>
-      <c r="E40" s="164"/>
-      <c r="F40" s="164"/>
-      <c r="G40" s="164"/>
-      <c r="H40" s="164"/>
-      <c r="I40" s="164"/>
-      <c r="J40" s="164"/>
-      <c r="K40" s="164"/>
-      <c r="L40" s="164"/>
-      <c r="M40" s="164"/>
-      <c r="N40" s="164"/>
-      <c r="O40" s="164"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="164"/>
-      <c r="E41" s="164"/>
-      <c r="F41" s="164"/>
-      <c r="G41" s="164"/>
-      <c r="H41" s="164"/>
-      <c r="I41" s="164"/>
-      <c r="J41" s="164"/>
-      <c r="K41" s="164"/>
-      <c r="L41" s="164"/>
-      <c r="M41" s="164"/>
-      <c r="N41" s="164"/>
-      <c r="O41" s="164"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="164"/>
-      <c r="E42" s="164"/>
-      <c r="F42" s="164"/>
-      <c r="G42" s="164"/>
-      <c r="H42" s="164"/>
-      <c r="I42" s="164"/>
-      <c r="J42" s="164"/>
-      <c r="K42" s="164"/>
-      <c r="L42" s="164"/>
-      <c r="M42" s="164"/>
-      <c r="N42" s="164"/>
-      <c r="O42" s="164"/>
-    </row>
-    <row r="43" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="164"/>
-      <c r="E43" s="164"/>
-      <c r="F43" s="164"/>
-      <c r="G43" s="164"/>
-      <c r="H43" s="164"/>
-      <c r="I43" s="164"/>
-      <c r="J43" s="164"/>
-      <c r="K43" s="164"/>
-      <c r="L43" s="164"/>
-      <c r="M43" s="164"/>
-      <c r="N43" s="164"/>
-      <c r="O43" s="164"/>
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="171" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" s="171"/>
+      <c r="F38" s="171"/>
+      <c r="G38" s="171"/>
+      <c r="H38" s="171"/>
+      <c r="I38" s="171"/>
+      <c r="J38" s="171"/>
+      <c r="K38" s="171"/>
+      <c r="L38" s="171"/>
+      <c r="M38" s="171"/>
+      <c r="N38" s="171"/>
+      <c r="O38" s="171"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="171"/>
+      <c r="E39" s="171"/>
+      <c r="F39" s="171"/>
+      <c r="G39" s="171"/>
+      <c r="H39" s="171"/>
+      <c r="I39" s="171"/>
+      <c r="J39" s="171"/>
+      <c r="K39" s="171"/>
+      <c r="L39" s="171"/>
+      <c r="M39" s="171"/>
+      <c r="N39" s="171"/>
+      <c r="O39" s="171"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="171"/>
+      <c r="E40" s="171"/>
+      <c r="F40" s="171"/>
+      <c r="G40" s="171"/>
+      <c r="H40" s="171"/>
+      <c r="I40" s="171"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="171"/>
+      <c r="L40" s="171"/>
+      <c r="M40" s="171"/>
+      <c r="N40" s="171"/>
+      <c r="O40" s="171"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="171"/>
+      <c r="E41" s="171"/>
+      <c r="F41" s="171"/>
+      <c r="G41" s="171"/>
+      <c r="H41" s="171"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
+      <c r="L41" s="171"/>
+      <c r="M41" s="171"/>
+      <c r="N41" s="171"/>
+      <c r="O41" s="171"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="171"/>
+      <c r="E42" s="171"/>
+      <c r="F42" s="171"/>
+      <c r="G42" s="171"/>
+      <c r="H42" s="171"/>
+      <c r="I42" s="171"/>
+      <c r="J42" s="171"/>
+      <c r="K42" s="171"/>
+      <c r="L42" s="171"/>
+      <c r="M42" s="171"/>
+      <c r="N42" s="171"/>
+      <c r="O42" s="171"/>
+    </row>
+    <row r="43" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D43" s="171"/>
+      <c r="E43" s="171"/>
+      <c r="F43" s="171"/>
+      <c r="G43" s="171"/>
+      <c r="H43" s="171"/>
+      <c r="I43" s="171"/>
+      <c r="J43" s="171"/>
+      <c r="K43" s="171"/>
+      <c r="L43" s="171"/>
+      <c r="M43" s="171"/>
+      <c r="N43" s="171"/>
+      <c r="O43" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D38:O43"/>
@@ -5092,11 +5043,6 @@
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -5106,16 +5052,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
   <dimension ref="C3:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C3" s="147" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C6" s="148" t="s">
-        <v>154</v>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="142" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="143" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/2026/COLOMBRES/Marzo/Marzo COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/Marzo/Marzo COLOMBRES 360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\COLOMBRES\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5713B3A-1550-4D55-B5B9-F1CA50C1FDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BCA038-F60D-4DED-8F40-0C431A47648E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$125</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="186">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -485,9 +485,6 @@
   </si>
   <si>
     <t>Punitorios mal cobrados 4A</t>
-  </si>
-  <si>
-    <t>Mes de FEBRERO</t>
   </si>
   <si>
     <t>Guenaga Gonzalo Federico</t>
@@ -503,21 +500,9 @@
 Alias: ALFA.CETRO.AMOROSAS</t>
   </si>
   <si>
-    <t>VTO 17/04</t>
-  </si>
-  <si>
     <t>Mes de MARZO</t>
   </si>
   <si>
-    <t>Frank Matias Wallace - Mantenimiento ascensor MARZO</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza -  Mes de MARZO</t>
-  </si>
-  <si>
-    <t>EL DPTO 2A REALIZO UN INGRESO DE $300.000 DE DONDE SE ABONO LOS HONORARIOS QUE CORRESPONDEN A LA FIRMA DEL CONVENIO ($120.000) Y LE RESTAN ABONAR 6 CUOTAS DE $400.000 CON VENCIMIENTO EN MARZO, ABRIL, JUNIO, AGOSTO, OCTUBRE Y MARZO DEL 2026 - DICHO DEPARTAMENTO ESTA COLOREADO DE GRIS YA QUE INGRESO EN UN PLAN DE PAGOS</t>
-  </si>
-  <si>
     <t>Fotocopias - Grafica Tuge</t>
   </si>
   <si>
@@ -530,9 +515,6 @@
     <t>Transf 12/03</t>
   </si>
   <si>
-    <t>Deposito ya identificado mes Enero (mal restados en expensas de Febrero)</t>
-  </si>
-  <si>
     <t>Debito 09/03</t>
   </si>
   <si>
@@ -542,9 +524,6 @@
     <t>Debito 10/03</t>
   </si>
   <si>
-    <t>Sotelo Gladys Patricia - Reemplazo Sr. Diego Calderon</t>
-  </si>
-  <si>
     <t>Seguro Federacion Patronal - Seguro de consorcio - Poliza nro. 2290715</t>
   </si>
   <si>
@@ -566,9 +545,6 @@
     <t>Debito 12/03</t>
   </si>
   <si>
-    <t>Allianz Consorcio Poliza - Debito poliza mes anterior (Febrero) - Se debita ultima cuota de esta poliza</t>
-  </si>
-  <si>
     <t>Debito 16/03</t>
   </si>
   <si>
@@ -581,9 +557,6 @@
     <t>Transf 27/03</t>
   </si>
   <si>
-    <t>Gustavo Padron Sr Contador - Balance anual pedido por RPAC</t>
-  </si>
-  <si>
     <t>Tofema - compra de portalamparas y lamapra</t>
   </si>
   <si>
@@ -593,13 +566,34 @@
     <t>Transf 30/03</t>
   </si>
   <si>
-    <t>Se adeuda Marzo</t>
-  </si>
-  <si>
     <t>Banco - Mantenimiento cuenta corriente - Supervielle por cierre ya que no estaba la chequwera y hubo que denunciar los cheques</t>
   </si>
   <si>
     <t>Bonificacion bancaria por parte de Santander</t>
+  </si>
+  <si>
+    <t>VTO 15/05</t>
+  </si>
+  <si>
+    <t>Mes de ABRIL</t>
+  </si>
+  <si>
+    <t>Se adeuda ABRIL</t>
+  </si>
+  <si>
+    <t>Frank Matias Wallace - Mantenimiento ascensor ABRIL</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza -  Mes de ABRIL</t>
+  </si>
+  <si>
+    <t>EL DPTO 2A REALIZO UN INGRESO DE $300.000 DE DONDE SE ABONO LOS HONORARIOS QUE CORRESPONDEN A LA FIRMA DEL CONVENIO ($120.000) Y LE RESTAN ABONAR 6 CUOTAS DE $400.000 CON VENCIMIENTO EN ABRIL, ABRIL, JUNIO, AGOSTO, OCTUBRE Y ABRIL DEL 2026 - DICHO DEPARTAMENTO ESTA COLOREADO DE GRIS YA QUE INGRESO EN UN PLAN DE PAGOS</t>
+  </si>
+  <si>
+    <t>Allianz Consorcio Poliza - Debito poliza mes anterior (MARZO) - Se debita ultima cuota de esta poliza</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado mes Enero (mal restados en expensas de MARZO)</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1232,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1460,130 +1454,129 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1972,7 +1965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2011,68 +2004,68 @@
       <c r="D3" s="109"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="162" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="162"/>
+      <c r="A4" s="181" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="181"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="162"/>
-      <c r="B5" s="162"/>
+      <c r="A5" s="181"/>
+      <c r="B5" s="181"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="162"/>
-      <c r="B6" s="162"/>
+      <c r="A6" s="181"/>
+      <c r="B6" s="181"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="162"/>
-      <c r="B7" s="162"/>
+      <c r="A7" s="181"/>
+      <c r="B7" s="181"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="159" t="s">
-        <v>155</v>
+      <c r="B9" s="180" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="159"/>
+      <c r="B10" s="180"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="159"/>
+      <c r="B11" s="180"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="163" t="s">
+      <c r="A14" s="182" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="163"/>
-      <c r="C14" s="163"/>
-      <c r="D14" s="163"/>
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="163"/>
-      <c r="B15" s="163"/>
-      <c r="C15" s="163"/>
-      <c r="D15" s="163"/>
+      <c r="A15" s="182"/>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="163"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="163"/>
-      <c r="D16" s="163"/>
+      <c r="A16" s="182"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="163"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="163"/>
-      <c r="D17" s="163"/>
+      <c r="A17" s="182"/>
+      <c r="B17" s="182"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2100,10 +2093,10 @@
         <v>127</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C23" s="136">
-        <v>1603651.83</v>
+        <v>1711920.96</v>
       </c>
       <c r="D23" s="80"/>
     </row>
@@ -2113,7 +2106,7 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="136">
-        <v>-820908.27</v>
+        <v>-707237.36</v>
       </c>
       <c r="D24" s="80"/>
     </row>
@@ -2123,7 +2116,7 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="136">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="D25" s="80"/>
       <c r="G25" s="152"/>
@@ -2141,7 +2134,7 @@
       <c r="B27" s="47"/>
       <c r="C27" s="106">
         <f>SUM(C23:C26)</f>
-        <v>782744</v>
+        <v>1004684</v>
       </c>
       <c r="D27" s="47"/>
     </row>
@@ -2150,10 +2143,10 @@
         <v>126</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C28" s="136">
-        <v>1547614.11</v>
+        <v>1504484.16</v>
       </c>
       <c r="D28" s="113"/>
     </row>
@@ -2163,7 +2156,7 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="136">
-        <v>-336606.06</v>
+        <v>-327225.28999999998</v>
       </c>
       <c r="D29" s="113"/>
     </row>
@@ -2173,14 +2166,14 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="136">
-        <v>0.95</v>
+        <v>0.13</v>
       </c>
       <c r="D30" s="113"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="198"/>
+      <c r="C31" s="160"/>
       <c r="D31" s="113"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2190,19 +2183,19 @@
       <c r="B32" s="112"/>
       <c r="C32" s="48">
         <f>SUM(C28:C31)</f>
-        <v>1211009</v>
+        <v>1177258.9999999998</v>
       </c>
       <c r="D32" s="81"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C33" s="136">
-        <v>1232494.5</v>
+        <v>1357095.49</v>
       </c>
       <c r="D33" s="113"/>
     </row>
@@ -2212,7 +2205,7 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="136">
-        <v>-268067.53000000003</v>
+        <v>-295168.25</v>
       </c>
       <c r="D34" s="113"/>
     </row>
@@ -2222,14 +2215,14 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="136">
-        <v>0.03</v>
+        <v>0.76</v>
       </c>
       <c r="D35" s="113"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="198"/>
+      <c r="C36" s="160"/>
       <c r="D36" s="113"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2239,854 +2232,831 @@
       <c r="B37" s="112"/>
       <c r="C37" s="48">
         <f>SUM(C33:C36)</f>
-        <v>964427</v>
+        <v>1061928</v>
       </c>
       <c r="D37" s="81"/>
       <c r="F37" s="14"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>168</v>
-      </c>
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="198">
-        <f>175000+300000+331000</f>
-        <v>806000</v>
-      </c>
+      <c r="C38" s="160"/>
       <c r="D38" s="113"/>
       <c r="F38" s="14"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="198"/>
+      <c r="C39" s="160"/>
       <c r="D39" s="113"/>
-      <c r="F39" s="14"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="198"/>
+      <c r="B40" s="159"/>
+      <c r="C40" s="160"/>
       <c r="D40" s="113"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="197"/>
-      <c r="C41" s="198"/>
-      <c r="D41" s="113"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="47" t="s">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="112"/>
-      <c r="C42" s="48">
-        <f>SUM(C38:C41)</f>
-        <v>806000</v>
-      </c>
-      <c r="D42" s="81"/>
-    </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="82">
-        <f>+C27+C32+C42+C37</f>
-        <v>3764180</v>
-      </c>
-      <c r="E43" s="14"/>
+      <c r="B41" s="112"/>
+      <c r="C41" s="48">
+        <f>SUM(C38:C40)</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="81"/>
+    </row>
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="82">
+        <f>+C27+C32+C41+C37</f>
+        <v>3243871</v>
+      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="26"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="83"/>
       <c r="F43" s="14"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="83"/>
-      <c r="F44" s="14"/>
-    </row>
-    <row r="45" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="56" t="s">
+    <row r="44" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="136">
+        <v>135000</v>
+      </c>
+      <c r="D44" s="123" t="s">
+        <v>156</v>
+      </c>
+      <c r="G44" s="14"/>
+    </row>
+    <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="107" t="s">
+        <v>180</v>
+      </c>
       <c r="C45" s="136">
+        <v>0</v>
+      </c>
+      <c r="D45" s="123"/>
+      <c r="G45" s="14"/>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="82">
+        <f>SUM(C44:C45)</f>
         <v>135000</v>
       </c>
-      <c r="D45" s="123" t="s">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" s="25"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="57"/>
+    </row>
+    <row r="48" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="176" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" s="177"/>
+      <c r="C48" s="155">
+        <v>125266</v>
+      </c>
+      <c r="D48" s="153" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="176" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" s="177"/>
+      <c r="C49" s="155">
+        <v>220076.23</v>
+      </c>
+      <c r="D49" s="153" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="176" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" s="177"/>
+      <c r="C50" s="156">
+        <v>4203</v>
+      </c>
+      <c r="D50" s="122" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" s="25"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="84">
+        <f>SUM(C48:C50)</f>
+        <v>349545.23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="139"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="85"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" s="80" t="s">
+        <v>154</v>
+      </c>
+      <c r="C53" s="165">
+        <v>1902538.49</v>
+      </c>
+      <c r="D53" s="119" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" s="116"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="80" t="s">
+        <v>160</v>
+      </c>
+      <c r="C54" s="165">
+        <v>305170.05</v>
+      </c>
+      <c r="D54" s="119" t="s">
         <v>161</v>
       </c>
-      <c r="G45" s="14"/>
-    </row>
-    <row r="46" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="B46" s="200"/>
-      <c r="C46" s="136">
-        <v>150000</v>
-      </c>
-      <c r="D46" s="123"/>
-      <c r="G46" s="14"/>
-    </row>
-    <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="115" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" s="107" t="s">
-        <v>185</v>
-      </c>
-      <c r="C47" s="136">
-        <v>0</v>
-      </c>
-      <c r="D47" s="123"/>
-      <c r="G47" s="14"/>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="18"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="82">
-        <f>SUM(C45:C47)</f>
-        <v>285000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B49" s="25"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="57"/>
-    </row>
-    <row r="50" spans="1:6" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="160" t="s">
-        <v>169</v>
-      </c>
-      <c r="B50" s="161"/>
-      <c r="C50" s="155">
-        <v>125266</v>
-      </c>
-      <c r="D50" s="153" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="160" t="s">
-        <v>176</v>
-      </c>
-      <c r="B51" s="161"/>
-      <c r="C51" s="155">
-        <v>220076.23</v>
-      </c>
-      <c r="D51" s="153" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="160" t="s">
-        <v>125</v>
-      </c>
-      <c r="B52" s="161"/>
-      <c r="C52" s="156">
-        <v>4203</v>
-      </c>
-      <c r="D52" s="122" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B53" s="25"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="84">
-        <f>SUM(C50:C52)</f>
-        <v>349545.23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" s="139"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="85"/>
+      <c r="F54" s="116"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="80" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="C55" s="204">
-        <v>1902538.49</v>
-      </c>
-      <c r="D55" s="119" t="s">
-        <v>165</v>
-      </c>
-      <c r="F55" s="116"/>
+        <v>154</v>
+      </c>
+      <c r="C55" s="140">
+        <v>22004.79</v>
+      </c>
+      <c r="D55" s="122" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="80" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B56" s="80" t="s">
-        <v>166</v>
-      </c>
-      <c r="C56" s="204">
-        <v>305170.05</v>
-      </c>
-      <c r="D56" s="119" t="s">
-        <v>167</v>
-      </c>
-      <c r="F56" s="116"/>
+        <v>154</v>
+      </c>
+      <c r="C56" s="140">
+        <v>198043.09</v>
+      </c>
+      <c r="D56" s="122" t="str">
+        <f>D55</f>
+        <v>Debito 12/03</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="80" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B57" s="80" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C57" s="140">
-        <v>22004.79</v>
-      </c>
-      <c r="D57" s="122" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="80" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="C58" s="140">
-        <v>198043.09</v>
-      </c>
-      <c r="D58" s="122" t="str">
-        <f>D57</f>
+        <v>408222.25</v>
+      </c>
+      <c r="D57" s="120" t="str">
+        <f>D56</f>
         <v>Debito 12/03</v>
       </c>
     </row>
+    <row r="58" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" s="139"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="84">
+        <f>SUM(C53:C57)</f>
+        <v>2835978.67</v>
+      </c>
+    </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="80" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="C59" s="140">
-        <v>408222.25</v>
-      </c>
-      <c r="D59" s="120" t="str">
-        <f>D58</f>
-        <v>Debito 12/03</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B60" s="139"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="84">
-        <f>SUM(C55:C59)</f>
-        <v>2835978.67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="24" t="s">
+      <c r="A59" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="139"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="85"/>
+      <c r="B59" s="139"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="85"/>
+    </row>
+    <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="80" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="80"/>
+      <c r="C60" s="140">
+        <v>598627.16</v>
+      </c>
+      <c r="D60" s="119" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="B61" s="80"/>
+      <c r="C61" s="140">
+        <v>9259.66</v>
+      </c>
+      <c r="D61" s="119" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="80" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B62" s="80"/>
       <c r="C62" s="140">
-        <v>598627.16</v>
-      </c>
-      <c r="D62" s="119" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="B63" s="80"/>
+        <v>0</v>
+      </c>
+      <c r="D62" s="119"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="178" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" s="179"/>
       <c r="C63" s="140">
-        <v>9259.66</v>
-      </c>
-      <c r="D63" s="119" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="80" t="s">
-        <v>134</v>
-      </c>
-      <c r="B64" s="80"/>
+        <v>204149</v>
+      </c>
+      <c r="D63" s="121" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="174" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="175"/>
       <c r="C64" s="140">
-        <v>0</v>
-      </c>
-      <c r="D64" s="119"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="169" t="s">
+        <v>100000</v>
+      </c>
+      <c r="D64" s="121" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="176" t="s">
+        <v>171</v>
+      </c>
+      <c r="B65" s="177"/>
+      <c r="C65" s="140">
+        <v>35200</v>
+      </c>
+      <c r="D65" s="121" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="25"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="84">
+        <f>SUM(C60:C65)</f>
+        <v>947235.82000000007</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B67" s="25"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="87"/>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="174" t="s">
+        <v>164</v>
+      </c>
+      <c r="B68" s="175"/>
+      <c r="C68" s="140">
+        <v>696297</v>
+      </c>
+      <c r="D68" s="119" t="s">
         <v>157</v>
       </c>
-      <c r="B65" s="170"/>
-      <c r="C65" s="140">
-        <v>204149</v>
-      </c>
-      <c r="D65" s="121" t="s">
+    </row>
+    <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="176" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" s="177"/>
+      <c r="C69" s="140">
+        <v>5720</v>
+      </c>
+      <c r="D69" s="121" t="s">
+        <v>149</v>
+      </c>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+    </row>
+    <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="161" t="s">
+        <v>174</v>
+      </c>
+      <c r="B70" s="158"/>
+      <c r="C70" s="140">
+        <v>250000</v>
+      </c>
+      <c r="D70" s="121" t="s">
+        <v>175</v>
+      </c>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+    </row>
+    <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="157" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="167" t="s">
+      <c r="B71" s="158"/>
+      <c r="C71" s="140">
+        <v>17983</v>
+      </c>
+      <c r="D71" s="121" t="s">
         <v>172</v>
-      </c>
-      <c r="B66" s="168"/>
-      <c r="C66" s="140">
-        <v>100000</v>
-      </c>
-      <c r="D66" s="121" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="160" t="s">
-        <v>179</v>
-      </c>
-      <c r="B67" s="161"/>
-      <c r="C67" s="140">
-        <v>35200</v>
-      </c>
-      <c r="D67" s="121" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B68" s="25"/>
-      <c r="C68" s="30"/>
-      <c r="D68" s="84">
-        <f>SUM(C62:C67)</f>
-        <v>947235.82000000007</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B69" s="25"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="87"/>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="167" t="s">
-        <v>171</v>
-      </c>
-      <c r="B70" s="168"/>
-      <c r="C70" s="140">
-        <v>696297</v>
-      </c>
-      <c r="D70" s="119" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="160" t="s">
-        <v>160</v>
-      </c>
-      <c r="B71" s="161"/>
-      <c r="C71" s="140">
-        <v>5720</v>
-      </c>
-      <c r="D71" s="121" t="s">
-        <v>149</v>
       </c>
       <c r="E71" s="39"/>
       <c r="F71" s="39"/>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="199" t="s">
-        <v>183</v>
-      </c>
-      <c r="B72" s="158"/>
+      <c r="A72" s="174" t="s">
+        <v>182</v>
+      </c>
+      <c r="B72" s="175"/>
       <c r="C72" s="140">
-        <v>250000</v>
+        <v>103950</v>
       </c>
       <c r="D72" s="121" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="E72" s="39"/>
       <c r="F72" s="39"/>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="157" t="s">
+      <c r="A73" s="174" t="s">
         <v>182</v>
       </c>
-      <c r="B73" s="158"/>
+      <c r="B73" s="175"/>
       <c r="C73" s="140">
-        <v>17983</v>
+        <v>100000</v>
       </c>
       <c r="D73" s="121" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E73" s="39"/>
       <c r="F73" s="39"/>
     </row>
-    <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="167" t="s">
-        <v>158</v>
-      </c>
-      <c r="B74" s="168"/>
-      <c r="C74" s="140">
-        <v>103950</v>
+    <row r="74" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="174" t="s">
+        <v>182</v>
+      </c>
+      <c r="B74" s="175"/>
+      <c r="C74" s="165">
+        <v>128900</v>
       </c>
       <c r="D74" s="121" t="s">
-        <v>161</v>
-      </c>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-    </row>
-    <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="167" t="s">
-        <v>158</v>
-      </c>
-      <c r="B75" s="168"/>
-      <c r="C75" s="140">
-        <v>100000</v>
-      </c>
-      <c r="D75" s="121" t="s">
-        <v>180</v>
-      </c>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-    </row>
-    <row r="76" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="167" t="s">
-        <v>158</v>
-      </c>
-      <c r="B76" s="168"/>
-      <c r="C76" s="204">
-        <v>128900</v>
-      </c>
-      <c r="D76" s="121" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="90">
-        <f>SUM(C70:C76)</f>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="90">
+        <f>SUM(C68:C74)</f>
         <v>1302850</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="24" t="s">
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B78" s="141"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="87"/>
-    </row>
-    <row r="79" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="160" t="s">
-        <v>186</v>
-      </c>
-      <c r="B79" s="161"/>
-      <c r="C79" s="140">
+      <c r="B76" s="141"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="87"/>
+    </row>
+    <row r="77" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="176" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" s="177"/>
+      <c r="C77" s="140">
         <f>2*65343</f>
         <v>130686</v>
       </c>
-      <c r="D79" s="91"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="80" t="s">
-        <v>178</v>
-      </c>
-      <c r="B80" s="80"/>
-      <c r="C80" s="140">
+      <c r="D77" s="91"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B78" s="80"/>
+      <c r="C78" s="140">
         <f>36414.42+127804.78</f>
         <v>164219.20000000001</v>
       </c>
-      <c r="D80" s="89"/>
-    </row>
-    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="44" t="s">
+      <c r="D78" s="89"/>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="B81" s="44"/>
-      <c r="C81" s="92"/>
-      <c r="D81" s="84">
-        <f>SUM(C79:C80)</f>
+      <c r="B79" s="44"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="84">
+        <f>SUM(C77:C78)</f>
         <v>294905.2</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="80"/>
-      <c r="D82" s="93"/>
-    </row>
-    <row r="83" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="164" t="s">
+    <row r="80" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="80"/>
+      <c r="D80" s="93"/>
+    </row>
+    <row r="81" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="171" t="s">
         <v>139</v>
       </c>
-      <c r="B83" s="165"/>
-      <c r="C83" s="166"/>
-      <c r="D83" s="94">
+      <c r="B81" s="172"/>
+      <c r="C81" s="173"/>
+      <c r="D81" s="94">
         <f>10000000-9779694.92</f>
         <v>220305.08000000007</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1"/>
+    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1"/>
+      <c r="C82" s="95"/>
+      <c r="D82" s="96"/>
+      <c r="E82" s="39"/>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" s="10"/>
+      <c r="C83" s="97"/>
+      <c r="D83" s="98">
+        <f>(SUM(D23:D81))</f>
+        <v>9329691</v>
+      </c>
+      <c r="E83" s="39"/>
+      <c r="F83" s="39"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C84" s="95"/>
-      <c r="D84" s="96"/>
-      <c r="E84" s="39"/>
+      <c r="D84" s="95"/>
+      <c r="F84" s="117"/>
     </row>
     <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B85" s="10"/>
-      <c r="C85" s="97"/>
-      <c r="D85" s="98">
-        <f>(SUM(D23:D83))</f>
-        <v>10000000</v>
-      </c>
-      <c r="E85" s="39"/>
-      <c r="F85" s="39"/>
+      <c r="C85" s="95"/>
+      <c r="D85" s="95"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C86" s="95"/>
-      <c r="D86" s="95"/>
-      <c r="F86" s="117"/>
-    </row>
-    <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C87" s="95"/>
-      <c r="D87" s="95"/>
+      <c r="A86" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" s="12"/>
+      <c r="C86" s="99"/>
+      <c r="D86" s="100"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="169"/>
+      <c r="B87" s="170"/>
+      <c r="C87" s="88"/>
+      <c r="D87" s="86"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B88" s="12"/>
-      <c r="C88" s="99"/>
-      <c r="D88" s="100"/>
+      <c r="A88" s="169"/>
+      <c r="B88" s="170"/>
+      <c r="C88" s="88"/>
+      <c r="D88" s="86"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="174"/>
-      <c r="B89" s="175"/>
+      <c r="A89" s="103"/>
+      <c r="B89" s="104"/>
       <c r="C89" s="88"/>
       <c r="D89" s="86"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="174"/>
-      <c r="B90" s="175"/>
-      <c r="C90" s="88"/>
-      <c r="D90" s="86"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="103"/>
-      <c r="B91" s="104"/>
-      <c r="C91" s="88"/>
-      <c r="D91" s="86"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="42"/>
-      <c r="B92" s="41"/>
-      <c r="C92" s="49"/>
-      <c r="D92" s="49">
-        <f>SUM(C89:C91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="20" t="s">
+      <c r="A90" s="42"/>
+      <c r="B90" s="41"/>
+      <c r="C90" s="49"/>
+      <c r="D90" s="49">
+        <f>SUM(C87:C89)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B95" s="20"/>
-      <c r="C95" s="21"/>
-      <c r="D95" s="124">
+      <c r="B93" s="20"/>
+      <c r="C93" s="21"/>
+      <c r="D93" s="124">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B95" s="10"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="58">
+        <f>D90+D93</f>
         <v>2000000</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="97" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B97" s="10"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="58">
-        <f>D92+D95</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A97" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B97" s="79">
+        <f>D83</f>
+        <v>9329691</v>
+      </c>
+      <c r="C97" s="39"/>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" s="79">
+        <f>D83-D81</f>
+        <v>9109385.9199999999</v>
+      </c>
+    </row>
     <row r="99" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="78" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B99" s="79">
-        <f>D85</f>
-        <v>10000000</v>
-      </c>
-      <c r="C99" s="39"/>
+        <f>D95-D93</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="78" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="B100" s="79">
-        <f>D85-D83</f>
-        <v>9779694.9199999999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="B101" s="79">
-        <f>D97-D95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="78" t="s">
-        <v>88</v>
-      </c>
-      <c r="B102" s="79">
-        <f>D97</f>
+        <f>D95</f>
         <v>2000000</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="173" t="s">
-        <v>159</v>
-      </c>
-      <c r="B105" s="173"/>
-      <c r="C105" s="173"/>
-      <c r="D105" s="173"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="173"/>
-      <c r="B106" s="173"/>
-      <c r="C106" s="173"/>
-      <c r="D106" s="173"/>
-    </row>
-    <row r="107" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="173"/>
-      <c r="B107" s="173"/>
-      <c r="C107" s="173"/>
-      <c r="D107" s="173"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="15" t="s">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="168" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103" s="168"/>
+      <c r="C103" s="168"/>
+      <c r="D103" s="168"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="168"/>
+      <c r="B104" s="168"/>
+      <c r="C104" s="168"/>
+      <c r="D104" s="168"/>
+    </row>
+    <row r="105" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="168"/>
+      <c r="B105" s="168"/>
+      <c r="C105" s="168"/>
+      <c r="D105" s="168"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B109" s="35"/>
-    </row>
-    <row r="110" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="23" t="s">
+      <c r="B107" s="35"/>
+    </row>
+    <row r="108" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B110" s="105">
+      <c r="B108" s="105">
         <v>7724336.4600000009</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B109" s="36">
+        <f>PRORRATEO!H35</f>
+        <v>12810228.029999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B110" s="89">
+        <f>B124</f>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B111" s="36">
-        <f>PRORRATEO!H35</f>
-        <v>12810228.029999999</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B112" s="89">
-        <f>B126</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B113" s="89">
+        <v>177</v>
+      </c>
+      <c r="B111" s="89">
         <v>400000</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="17" t="s">
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B114" s="118">
+      <c r="B112" s="118">
         <f>-1231-13491-11006-8098</f>
         <v>-33826</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="17" t="s">
-        <v>164</v>
+    <row r="113" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B113" s="118">
+        <v>-240000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B114" s="118">
+        <v>-260000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" s="34" t="s">
+        <v>44</v>
       </c>
       <c r="B115" s="118">
-        <v>-240000</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <f>-B98</f>
+        <v>-9109385.9199999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B116" s="118">
-        <v>-260000</v>
+        <v>45</v>
+      </c>
+      <c r="B116" s="89">
+        <f>-(B99)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="B117" s="118">
-        <f>-B100</f>
-        <v>-9779694.9199999999</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B118" s="89">
-        <f>-(B101)</f>
-        <v>0</v>
-      </c>
+      <c r="A117" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="105">
+        <f>SUM(B108:B116)</f>
+        <v>11291352.570000002</v>
+      </c>
+      <c r="D117" s="162"/>
+    </row>
+    <row r="118" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="37"/>
+      <c r="C118" s="39"/>
+      <c r="E118" s="164"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="22" t="s">
+      <c r="D119" s="163"/>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" s="167" t="s">
+        <v>78</v>
+      </c>
+      <c r="B120" s="167"/>
+    </row>
+    <row r="121" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="167"/>
+      <c r="B121" s="167"/>
+    </row>
+    <row r="122" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="101"/>
+      <c r="B122" s="29"/>
+    </row>
+    <row r="123" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="101"/>
+      <c r="B123" s="29"/>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B119" s="105">
-        <f>SUM(B110:B118)</f>
-        <v>10621043.570000002</v>
-      </c>
-      <c r="D119" s="201"/>
-    </row>
-    <row r="120" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="37"/>
-      <c r="C120" s="39"/>
-      <c r="E120" s="203"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D121" s="202"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="172" t="s">
-        <v>78</v>
-      </c>
-      <c r="B122" s="172"/>
-    </row>
-    <row r="123" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="172"/>
-      <c r="B123" s="172"/>
-    </row>
-    <row r="124" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="101"/>
-      <c r="B124" s="29"/>
-    </row>
-    <row r="125" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="101"/>
-      <c r="B125" s="29"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B126" s="102">
-        <f>SUM(B124:B125)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L127" s="8"/>
-    </row>
-    <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="171"/>
-      <c r="B128" s="171"/>
-      <c r="C128" s="171"/>
-      <c r="D128" s="171"/>
+      <c r="B124" s="102">
+        <f>SUM(B122:B123)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L125" s="8"/>
+    </row>
+    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="166"/>
+      <c r="B126" s="166"/>
+      <c r="C126" s="166"/>
+      <c r="D126" s="166"/>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" s="166"/>
+      <c r="B127" s="166"/>
+      <c r="C127" s="166"/>
+      <c r="D127" s="166"/>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" s="166"/>
+      <c r="B128" s="166"/>
+      <c r="C128" s="166"/>
+      <c r="D128" s="166"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="171"/>
-      <c r="B129" s="171"/>
-      <c r="C129" s="171"/>
-      <c r="D129" s="171"/>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="171"/>
-      <c r="B130" s="171"/>
-      <c r="C130" s="171"/>
-      <c r="D130" s="171"/>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="171"/>
-      <c r="B131" s="171"/>
-      <c r="C131" s="171"/>
-      <c r="D131" s="171"/>
+      <c r="A129" s="166"/>
+      <c r="B129" s="166"/>
+      <c r="C129" s="166"/>
+      <c r="D129" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A128:D131"/>
-    <mergeCell ref="A122:B123"/>
-    <mergeCell ref="A105:D107"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A126:D129"/>
+    <mergeCell ref="A120:B121"/>
+    <mergeCell ref="A103:D105"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A87:B87"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3122,7 +3092,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="176" t="str">
+      <c r="B1" s="189" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco Santander
 Tipo de cuenta: Cuenta corriente en pesos
@@ -3130,15 +3100,15 @@
 CBU: 0720039720000002345040
 Alias: ALFA.CETRO.AMOROSAS</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
+      <c r="J1" s="189"/>
+      <c r="K1" s="189"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -3147,16 +3117,16 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="176"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="176"/>
-      <c r="F2" s="176"/>
-      <c r="G2" s="176"/>
-      <c r="H2" s="176"/>
-      <c r="I2" s="176"/>
-      <c r="J2" s="176"/>
-      <c r="K2" s="176"/>
+      <c r="B2" s="189"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="189"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="189"/>
+      <c r="K2" s="189"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -3170,16 +3140,16 @@
     </row>
     <row r="3" spans="1:19" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="177"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="177"/>
-      <c r="K3" s="177"/>
+      <c r="B3" s="190"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="190"/>
+      <c r="J3" s="190"/>
+      <c r="K3" s="190"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3191,76 +3161,76 @@
       <c r="P3" s="50"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="193" t="s">
+      <c r="A4" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="180" t="s">
+      <c r="C4" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="180" t="s">
+      <c r="D4" s="187" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="180" t="s">
+      <c r="E4" s="187" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="180" t="s">
+      <c r="F4" s="187" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="180" t="s">
+      <c r="G4" s="187" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="180" t="s">
+      <c r="H4" s="187" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="180" t="s">
+      <c r="I4" s="187" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="185" t="s">
+      <c r="J4" s="196" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="182" t="s">
+      <c r="K4" s="194" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="182" t="s">
+      <c r="L4" s="194" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="182" t="s">
+      <c r="M4" s="194" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="188" t="s">
+      <c r="N4" s="199" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="178" t="s">
+      <c r="P4" s="191" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="194"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="186"/>
-      <c r="K5" s="183"/>
-      <c r="L5" s="187"/>
-      <c r="M5" s="183"/>
-      <c r="N5" s="189"/>
+      <c r="A5" s="184"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="193"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="193"/>
+      <c r="J5" s="197"/>
+      <c r="K5" s="195"/>
+      <c r="L5" s="198"/>
+      <c r="M5" s="195"/>
+      <c r="N5" s="200"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 17/04</v>
-      </c>
-      <c r="P5" s="179"/>
+        <v>VTO 15/05</v>
+      </c>
+      <c r="P5" s="192"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3436,11 +3406,11 @@
     </row>
     <row r="9" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="190" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="191"/>
-      <c r="D9" s="192"/>
+      <c r="B9" s="201" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="202"/>
+      <c r="D9" s="203"/>
       <c r="E9" s="127"/>
       <c r="F9" s="128"/>
       <c r="G9" s="129"/>
@@ -4938,98 +4908,93 @@
     </row>
     <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="171" t="s">
+      <c r="D38" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="E38" s="171"/>
-      <c r="F38" s="171"/>
-      <c r="G38" s="171"/>
-      <c r="H38" s="171"/>
-      <c r="I38" s="171"/>
-      <c r="J38" s="171"/>
-      <c r="K38" s="171"/>
-      <c r="L38" s="171"/>
-      <c r="M38" s="171"/>
-      <c r="N38" s="171"/>
-      <c r="O38" s="171"/>
+      <c r="E38" s="166"/>
+      <c r="F38" s="166"/>
+      <c r="G38" s="166"/>
+      <c r="H38" s="166"/>
+      <c r="I38" s="166"/>
+      <c r="J38" s="166"/>
+      <c r="K38" s="166"/>
+      <c r="L38" s="166"/>
+      <c r="M38" s="166"/>
+      <c r="N38" s="166"/>
+      <c r="O38" s="166"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="171"/>
-      <c r="E39" s="171"/>
-      <c r="F39" s="171"/>
-      <c r="G39" s="171"/>
-      <c r="H39" s="171"/>
-      <c r="I39" s="171"/>
-      <c r="J39" s="171"/>
-      <c r="K39" s="171"/>
-      <c r="L39" s="171"/>
-      <c r="M39" s="171"/>
-      <c r="N39" s="171"/>
-      <c r="O39" s="171"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="166"/>
+      <c r="H39" s="166"/>
+      <c r="I39" s="166"/>
+      <c r="J39" s="166"/>
+      <c r="K39" s="166"/>
+      <c r="L39" s="166"/>
+      <c r="M39" s="166"/>
+      <c r="N39" s="166"/>
+      <c r="O39" s="166"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="171"/>
-      <c r="E40" s="171"/>
-      <c r="F40" s="171"/>
-      <c r="G40" s="171"/>
-      <c r="H40" s="171"/>
-      <c r="I40" s="171"/>
-      <c r="J40" s="171"/>
-      <c r="K40" s="171"/>
-      <c r="L40" s="171"/>
-      <c r="M40" s="171"/>
-      <c r="N40" s="171"/>
-      <c r="O40" s="171"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="166"/>
+      <c r="F40" s="166"/>
+      <c r="G40" s="166"/>
+      <c r="H40" s="166"/>
+      <c r="I40" s="166"/>
+      <c r="J40" s="166"/>
+      <c r="K40" s="166"/>
+      <c r="L40" s="166"/>
+      <c r="M40" s="166"/>
+      <c r="N40" s="166"/>
+      <c r="O40" s="166"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="171"/>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="171"/>
-      <c r="H41" s="171"/>
-      <c r="I41" s="171"/>
-      <c r="J41" s="171"/>
-      <c r="K41" s="171"/>
-      <c r="L41" s="171"/>
-      <c r="M41" s="171"/>
-      <c r="N41" s="171"/>
-      <c r="O41" s="171"/>
+      <c r="D41" s="166"/>
+      <c r="E41" s="166"/>
+      <c r="F41" s="166"/>
+      <c r="G41" s="166"/>
+      <c r="H41" s="166"/>
+      <c r="I41" s="166"/>
+      <c r="J41" s="166"/>
+      <c r="K41" s="166"/>
+      <c r="L41" s="166"/>
+      <c r="M41" s="166"/>
+      <c r="N41" s="166"/>
+      <c r="O41" s="166"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="171"/>
-      <c r="E42" s="171"/>
-      <c r="F42" s="171"/>
-      <c r="G42" s="171"/>
-      <c r="H42" s="171"/>
-      <c r="I42" s="171"/>
-      <c r="J42" s="171"/>
-      <c r="K42" s="171"/>
-      <c r="L42" s="171"/>
-      <c r="M42" s="171"/>
-      <c r="N42" s="171"/>
-      <c r="O42" s="171"/>
+      <c r="D42" s="166"/>
+      <c r="E42" s="166"/>
+      <c r="F42" s="166"/>
+      <c r="G42" s="166"/>
+      <c r="H42" s="166"/>
+      <c r="I42" s="166"/>
+      <c r="J42" s="166"/>
+      <c r="K42" s="166"/>
+      <c r="L42" s="166"/>
+      <c r="M42" s="166"/>
+      <c r="N42" s="166"/>
+      <c r="O42" s="166"/>
     </row>
     <row r="43" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="171"/>
-      <c r="E43" s="171"/>
-      <c r="F43" s="171"/>
-      <c r="G43" s="171"/>
-      <c r="H43" s="171"/>
-      <c r="I43" s="171"/>
-      <c r="J43" s="171"/>
-      <c r="K43" s="171"/>
-      <c r="L43" s="171"/>
-      <c r="M43" s="171"/>
-      <c r="N43" s="171"/>
-      <c r="O43" s="171"/>
+      <c r="D43" s="166"/>
+      <c r="E43" s="166"/>
+      <c r="F43" s="166"/>
+      <c r="G43" s="166"/>
+      <c r="H43" s="166"/>
+      <c r="I43" s="166"/>
+      <c r="J43" s="166"/>
+      <c r="K43" s="166"/>
+      <c r="L43" s="166"/>
+      <c r="M43" s="166"/>
+      <c r="N43" s="166"/>
+      <c r="O43" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D38:O43"/>
@@ -5043,6 +5008,11 @@
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
